--- a/reports/latest_backtest_dashboard.xlsx
+++ b/reports/latest_backtest_dashboard.xlsx
@@ -190,12 +190,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -654,23 +654,23 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>trend_scalp_nw (EMA5/21) [5m]</t>
+          <t>vwap_ema_momentum (EMA9/13) [60m]</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>289.63</v>
+        <v>714.63</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>-0.02718449608801872</v>
+        <v>-0.04624032870879385</v>
       </c>
     </row>
     <row r="5">
@@ -681,7 +681,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>trend_scalp_nw (EMA5/21) [5m]</t>
+          <t>trend_scalp_nw (EMA5/21) [1m]</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -691,13 +691,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>-1614.72</v>
+        <v>-1162.41</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>-0.08073600000000006</v>
+        <v>-0.05812049999999982</v>
       </c>
     </row>
     <row r="6">
@@ -708,7 +708,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>trend_scalp_nw (EMA8/21) [5m]</t>
+          <t>trend_scalp_nw (EMA9/21) [1m]</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -718,13 +718,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>-1332.18</v>
+        <v>-1335.02</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>-0.06660900000000002</v>
+        <v>-0.06675100000000002</v>
       </c>
     </row>
     <row r="7">
@@ -739,19 +739,19 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>-2657.27</v>
+        <v>-1782.8</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.1607565938469046</v>
+        <v>-0.1612290113873062</v>
       </c>
     </row>
     <row r="9">
@@ -773,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -796,7 +796,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NIFTY -- best: trend_scalp_nw (EMA5/21) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>NIFTY -- best: vwap_ema_momentum (EMA9/13) [60m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
@@ -886,550 +886,497 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="4" t="n"/>
+        <v>2026</v>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>0.007486499999999999</v>
+      </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
+      <c r="E5" s="13" t="n">
+        <v>0.007542532827983304</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>0.05840394725370424</v>
+      </c>
       <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
+      <c r="H5" s="14" t="n">
+        <v>-0.01546998917040258</v>
+      </c>
       <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="13" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="L5" s="14" t="n">
-        <v>-0.01893772098398157</v>
-      </c>
+      <c r="J5" s="14" t="n">
+        <v>-0.02081635547151973</v>
+      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="15" t="n">
-        <v>-0.003744500000000039</v>
+        <v>0.03573149999999981</v>
       </c>
       <c r="O5" s="16" t="n">
-        <v>-74.89</v>
+        <v>714.63</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>-0.0003804244995385213</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>0.02161964862108907</v>
-      </c>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="14" t="n">
-        <v>-0.01204925855631031</v>
-      </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="13" t="n">
-        <v>0.02763772101222905</v>
-      </c>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="14" t="n">
-        <v>-0.01785845673657797</v>
-      </c>
-      <c r="J6" s="4" t="n"/>
+      <c r="E6" s="15" t="n">
+        <v>0.007542532827983304</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>0.05840394725370424</v>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="17" t="n">
+        <v>-0.01546998917040258</v>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="17" t="n">
+        <v>-0.02081635547151973</v>
+      </c>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="17" t="n">
-        <v>0.01829450376936426</v>
-      </c>
-      <c r="O6" s="18" t="n">
-        <v>364.52</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="n">
-        <v>-0.0003804244995385213</v>
-      </c>
-      <c r="C7" s="17" t="n">
-        <v>0.02161964862108907</v>
-      </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="15" t="n">
-        <v>-0.01204925855631031</v>
-      </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="17" t="n">
-        <v>0.02763772101222905</v>
-      </c>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="15" t="n">
-        <v>-0.01785845673657797</v>
-      </c>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="17" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="L7" s="15" t="n">
-        <v>-0.01893772098398157</v>
-      </c>
-      <c r="M7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jan</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="18" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>149.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2025-Oct</t>
+          <t>2026-Apr</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="C11" s="4" t="n"/>
+        <v>0.02240377414486447</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>-0.01453558925808061</v>
+      </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="19" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>309.73</v>
+      <c r="H11" s="18" t="n">
+        <v>0.007542532827983304</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>151.98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2025-Nov</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="n">
-        <v>-0.01608834780176792</v>
-      </c>
-      <c r="C12" s="14" t="n">
-        <v>-0.002895964465760363</v>
-      </c>
+          <t>2026-May</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>0.05840394725370424</v>
+      </c>
+      <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="20" t="n">
-        <v>-0.01893772098398157</v>
+      <c r="H12" s="18" t="n">
+        <v>0.05840394725370424</v>
       </c>
       <c r="I12" s="16" t="n">
-        <v>-384.62</v>
+        <v>1185.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-Jan</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="n">
-        <v>0.01290682962352529</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>-0.01311794306688838</v>
-      </c>
+          <t>2026-Jul</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>-0.01546998917040258</v>
+      </c>
+      <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
-      <c r="H13" s="20" t="n">
-        <v>-0.0003804244995385213</v>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>-7.58</v>
+      <c r="H13" s="19" t="n">
+        <v>-0.01546998917040258</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>-332.41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-Feb</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>0.02161964862108907</v>
-      </c>
-      <c r="C14" s="4" t="n"/>
+          <t>2026-Sep</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>-0.012097376506736</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>-0.008825747353472017</v>
+      </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="19" t="n">
-        <v>0.02161964862108907</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>430.61</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2026-Apr</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="n">
-        <v>-0.01204925855631031</v>
-      </c>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="20" t="n">
-        <v>-0.01204925855631031</v>
-      </c>
-      <c r="I15" s="16" t="n">
-        <v>-245.18</v>
+        <v>-0.02081635547151973</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>-440.37</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jun</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n">
-        <v>0.01282945397095752</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>0.01462069155198182</v>
-      </c>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="19" t="n">
-        <v>0.02763772101222905</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>555.6</v>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026-Aug</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n">
-        <v>-0.01785845673657797</v>
-      </c>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="20" t="n">
-        <v>-0.01785845673657797</v>
-      </c>
-      <c r="I17" s="16" t="n">
-        <v>-368.93</v>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>19-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="13" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="18" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>149.73</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>06-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="13" t="n">
+        <v>0.02240377414486447</v>
+      </c>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="18" t="n">
+        <v>0.02240377414486447</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>451.43</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="14" t="n">
+        <v>-0.01453558925808061</v>
+      </c>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="19" t="n">
+        <v>-0.01453558925808061</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>-299.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>06-Oct-2025</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="C21" s="4" t="n"/>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="13" t="n">
+        <v>0.05840394725370424</v>
+      </c>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
-      <c r="G21" s="19" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="H21" s="18" t="n">
-        <v>309.73</v>
+      <c r="G21" s="18" t="n">
+        <v>0.05840394725370424</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>1185.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>10-Nov-2025</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
       <c r="C22" s="14" t="n">
-        <v>-0.01608834780176792</v>
+        <v>-0.01546998917040258</v>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="20" t="n">
-        <v>-0.01608834780176792</v>
-      </c>
-      <c r="H22" s="16" t="n">
-        <v>-326.75</v>
+      <c r="G22" s="19" t="n">
+        <v>-0.01546998917040258</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>-332.41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>24-Nov-2025</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="n">
-        <v>0.01526098710002212</v>
-      </c>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n"/>
       <c r="C23" s="14" t="n">
-        <v>-0.01788402371063795</v>
+        <v>-0.012097376506736</v>
       </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
-      <c r="G23" s="20" t="n">
-        <v>-0.002895964465760363</v>
-      </c>
-      <c r="H23" s="16" t="n">
-        <v>-57.87</v>
+      <c r="G23" s="19" t="n">
+        <v>-0.012097376506736</v>
+      </c>
+      <c r="H23" s="20" t="n">
+        <v>-255.92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>12-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="n">
-        <v>0.01290682962352529</v>
-      </c>
-      <c r="C24" s="4" t="n"/>
+          <t>14-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="14" t="n">
+        <v>-0.008825747353472017</v>
+      </c>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="19" t="n">
-        <v>0.01290682962352529</v>
-      </c>
-      <c r="H24" s="18" t="n">
-        <v>257.17</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>26-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="14" t="n">
-        <v>-0.01311794306688838</v>
-      </c>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="19" t="n">
-        <v>0.008218100234463109</v>
-      </c>
-      <c r="H25" s="18" t="n">
-        <v>165.86</v>
+        <v>-0.008825747353472017</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <v>-184.45</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>20-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="n">
-        <v>-0.01204925855631031</v>
-      </c>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="20" t="n">
-        <v>-0.01204925855631031</v>
-      </c>
-      <c r="H26" s="16" t="n">
-        <v>-245.18</v>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="n">
-        <v>0.01282945397095752</v>
-      </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="19" t="n">
-        <v>0.01282945397095752</v>
-      </c>
-      <c r="H27" s="18" t="n">
-        <v>257.91</v>
-      </c>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="23" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="n">
-        <v>0.01462069155198182</v>
-      </c>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="19" t="n">
-        <v>0.01462069155198182</v>
-      </c>
-      <c r="H28" s="18" t="n">
-        <v>297.69</v>
-      </c>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>5 (41.7%)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="23" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>10-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="14" t="n">
-        <v>-0.01785845673657797</v>
-      </c>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="20" t="n">
-        <v>-0.01785845673657797</v>
-      </c>
-      <c r="H29" s="16" t="n">
-        <v>-368.93</v>
-      </c>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>7 (58.3%)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="23" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="n">
+        <v>714.63</v>
+      </c>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="23" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="n">
+        <v>2338.58</v>
+      </c>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="23" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B32" s="21" t="n">
-        <v>13</v>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n">
+        <v>-1623.95</v>
       </c>
       <c r="C32" s="22" t="n"/>
       <c r="D32" s="23" t="n"/>
@@ -1437,13 +1384,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B33" s="24" t="inlineStr">
-        <is>
-          <t>7 (53.8%)</t>
-        </is>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="n">
+        <v>335.62</v>
       </c>
       <c r="C33" s="22" t="n"/>
       <c r="D33" s="23" t="n"/>
@@ -1451,13 +1396,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B34" s="24" t="inlineStr">
-        <is>
-          <t>6 (46.2%)</t>
-        </is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="n">
+        <v>59.55</v>
       </c>
       <c r="C34" s="22" t="n"/>
       <c r="D34" s="23" t="n"/>
@@ -1465,11 +1408,11 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B35" s="25" t="n">
-        <v>289.63</v>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B35" s="28" t="n">
+        <v>5.84</v>
       </c>
       <c r="C35" s="22" t="n"/>
       <c r="D35" s="23" t="n"/>
@@ -1477,11 +1420,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
+          <t>Avg Win (Rs)</t>
         </is>
       </c>
       <c r="B36" s="25" t="n">
-        <v>2174.65</v>
+        <v>467.72</v>
       </c>
       <c r="C36" s="22" t="n"/>
       <c r="D36" s="23" t="n"/>
@@ -1489,11 +1432,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B37" s="26" t="n">
-        <v>-1885.02</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B37" s="29" t="n">
+        <v>54.93</v>
       </c>
       <c r="C37" s="22" t="n"/>
       <c r="D37" s="23" t="n"/>
@@ -1501,11 +1444,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="27" t="n">
-        <v>863.12</v>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n">
+        <v>-231.99</v>
       </c>
       <c r="C38" s="22" t="n"/>
       <c r="D38" s="23" t="n"/>
@@ -1513,11 +1456,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B39" s="25" t="n">
-        <v>22.28</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="n">
+        <v>-29.23</v>
       </c>
       <c r="C39" s="22" t="n"/>
       <c r="D39" s="23" t="n"/>
@@ -1525,11 +1468,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B40" s="28" t="n">
-        <v>1.77</v>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="n">
+        <v>552.97</v>
       </c>
       <c r="C40" s="22" t="n"/>
       <c r="D40" s="23" t="n"/>
@@ -1537,11 +1480,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="n">
-        <v>310.66</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="n">
+        <v>-332.41</v>
       </c>
       <c r="C41" s="22" t="n"/>
       <c r="D41" s="23" t="n"/>
@@ -1549,11 +1492,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B42" s="29" t="n">
-        <v>16.01</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="23" t="n"/>
@@ -1561,11 +1504,11 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B43" s="26" t="n">
-        <v>-314.17</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B43" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="C43" s="22" t="n"/>
       <c r="D43" s="23" t="n"/>
@@ -1573,11 +1516,11 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B44" s="30" t="n">
-        <v>-14.84</v>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B44" s="26" t="n">
+        <v>-332.41</v>
       </c>
       <c r="C44" s="22" t="n"/>
       <c r="D44" s="23" t="n"/>
@@ -1585,11 +1528,11 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="n">
-        <v>406.75</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="n">
+        <v>-1004.29</v>
       </c>
       <c r="C45" s="22" t="n"/>
       <c r="D45" s="23" t="n"/>
@@ -1597,11 +1540,11 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B46" s="26" t="n">
-        <v>-368.93</v>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B46" s="30" t="n">
+        <v>-4.62</v>
       </c>
       <c r="C46" s="22" t="n"/>
       <c r="D46" s="23" t="n"/>
@@ -1609,11 +1552,11 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B47" s="21" t="n">
-        <v>2</v>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B47" s="31" t="n">
+        <v>0.71</v>
       </c>
       <c r="C47" s="22" t="n"/>
       <c r="D47" s="23" t="n"/>
@@ -1621,11 +1564,11 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B48" s="21" t="n">
-        <v>2</v>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B48" s="31" t="n">
+        <v>1.44</v>
       </c>
       <c r="C48" s="22" t="n"/>
       <c r="D48" s="23" t="n"/>
@@ -1633,11 +1576,11 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B49" s="26" t="n">
-        <v>-368.93</v>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B49" s="31" t="n">
+        <v>2.02</v>
       </c>
       <c r="C49" s="22" t="n"/>
       <c r="D49" s="23" t="n"/>
@@ -1645,77 +1588,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B50" s="26" t="n">
-        <v>-561.76</v>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B50" s="31" t="n">
+        <v>3.36</v>
       </c>
       <c r="C50" s="22" t="n"/>
       <c r="D50" s="23" t="n"/>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B51" s="30" t="n">
-        <v>-2.72</v>
-      </c>
-      <c r="C51" s="22" t="n"/>
-      <c r="D51" s="23" t="n"/>
-    </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B52" s="31" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="23" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B53" s="31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="C53" s="22" t="n"/>
-      <c r="D53" s="23" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B54" s="31" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="C54" s="22" t="n"/>
-      <c r="D54" s="23" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B55" s="31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="C55" s="22" t="n"/>
-      <c r="D55" s="23" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -1725,25 +1608,25 @@
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="B48:D48"/>
@@ -1759,7 +1642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1782,7 +1665,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANKNIFTY -- best: trend_scalp_nw (EMA5/21) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>BANKNIFTY -- best: trend_scalp_nw (EMA5/21) [1m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1755,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="4" t="n"/>
@@ -1880,336 +1763,308 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
+      <c r="H5" s="14" t="n">
+        <v>-0.0348495</v>
+      </c>
       <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
+      <c r="J5" s="14" t="n">
+        <v>-0.02411126554874084</v>
+      </c>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="14" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="N5" s="15" t="n">
-        <v>-0.03550450000000005</v>
-      </c>
-      <c r="O5" s="16" t="n">
-        <v>-710.09</v>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="17" t="n">
+        <v>-0.05812050000000002</v>
+      </c>
+      <c r="O5" s="20" t="n">
+        <v>-1162.41</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="14" t="n">
-        <v>-0.02995409697673192</v>
-      </c>
-      <c r="J6" s="4" t="n"/>
+      <c r="H6" s="17" t="n">
+        <v>-0.0348495</v>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="17" t="n">
+        <v>-0.02411126554874084</v>
+      </c>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="15" t="n">
-        <v>-0.04689653813833239</v>
-      </c>
-      <c r="O6" s="16" t="n">
-        <v>-904.63</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="15" t="n">
-        <v>-0.02995409697673192</v>
-      </c>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="15" t="n">
-        <v>-0.0355045</v>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jul</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>-0.024971</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>-0.01013149352480798</v>
+      </c>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="19" t="n">
+        <v>-0.0348495</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>-696.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2025-Dec</t>
+          <t>2026-Sep</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>-0.0355045</v>
+        <v>-0.02411126554874084</v>
       </c>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="20" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>-710.09</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jan</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="20" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>-336.91</v>
+      <c r="H11" s="19" t="n">
+        <v>-0.02411126554874084</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>-465.42</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-Aug</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>-0.01872526776763573</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>-0.01144310440313796</v>
-      </c>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="20" t="n">
-        <v>-0.02995409697673192</v>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>-567.72</v>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>13-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="14" t="n">
+        <v>-0.024971</v>
+      </c>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="19" t="n">
+        <v>-0.024971</v>
+      </c>
+      <c r="H15" s="20" t="n">
+        <v>-499.42</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>27-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="14" t="n">
+        <v>-0.01013149352480798</v>
+      </c>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="19" t="n">
+        <v>-0.01013149352480798</v>
+      </c>
+      <c r="H16" s="20" t="n">
+        <v>-197.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>29-Dec-2025</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
       <c r="C17" s="14" t="n">
-        <v>-0.0355045</v>
+        <v>-0.02411126554874084</v>
       </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
-      <c r="G17" s="20" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="H17" s="16" t="n">
-        <v>-710.09</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>26-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="14" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="20" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="H18" s="16" t="n">
-        <v>-336.91</v>
+      <c r="G17" s="19" t="n">
+        <v>-0.02411126554874084</v>
+      </c>
+      <c r="H17" s="20" t="n">
+        <v>-465.42</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>10-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="14" t="n">
-        <v>-0.01872526776763573</v>
-      </c>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="20" t="n">
-        <v>-0.01872526776763573</v>
-      </c>
-      <c r="H19" s="16" t="n">
-        <v>-354.9</v>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>24-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="14" t="n">
-        <v>-0.01144310440313796</v>
-      </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="20" t="n">
-        <v>-0.01144310440313796</v>
-      </c>
-      <c r="H20" s="16" t="n">
-        <v>-212.82</v>
-      </c>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="23" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="23" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>5 (100.0%)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="23" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="n">
-        <v>5</v>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="n">
+        <v>-1162.41</v>
       </c>
       <c r="C23" s="22" t="n"/>
       <c r="D23" s="23" t="n"/>
@@ -2217,13 +2072,11 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="C24" s="22" t="n"/>
       <c r="D24" s="23" t="n"/>
@@ -2231,13 +2084,11 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>5 (100.0%)</t>
-        </is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n">
+        <v>-1162.41</v>
       </c>
       <c r="C25" s="22" t="n"/>
       <c r="D25" s="23" t="n"/>
@@ -2245,11 +2096,11 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B26" s="26" t="n">
-        <v>-1614.72</v>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="n">
+        <v>236.31</v>
       </c>
       <c r="C26" s="22" t="n"/>
       <c r="D26" s="23" t="n"/>
@@ -2257,11 +2108,11 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B27" s="25" t="n">
-        <v>0</v>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n">
+        <v>-232.48</v>
       </c>
       <c r="C27" s="22" t="n"/>
       <c r="D27" s="23" t="n"/>
@@ -2269,11 +2120,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="n">
-        <v>-1614.72</v>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="n">
+        <v>-14.84</v>
       </c>
       <c r="C28" s="22" t="n"/>
       <c r="D28" s="23" t="n"/>
@@ -2281,11 +2132,11 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="n">
-        <v>328.47</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="C29" s="22" t="n"/>
       <c r="D29" s="23" t="n"/>
@@ -2293,11 +2144,11 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="n">
-        <v>-322.94</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B30" s="29" t="n">
+        <v>0</v>
       </c>
       <c r="C30" s="22" t="n"/>
       <c r="D30" s="23" t="n"/>
@@ -2305,11 +2156,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B31" s="28" t="n">
-        <v>-14.84</v>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n">
+        <v>-232.48</v>
       </c>
       <c r="C31" s="22" t="n"/>
       <c r="D31" s="23" t="n"/>
@@ -2317,11 +2168,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="n">
-        <v>0</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="n">
+        <v>-14.84</v>
       </c>
       <c r="C32" s="22" t="n"/>
       <c r="D32" s="23" t="n"/>
@@ -2329,11 +2180,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B33" s="29" t="n">
-        <v>0</v>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="n">
+        <v>-197.57</v>
       </c>
       <c r="C33" s="22" t="n"/>
       <c r="D33" s="23" t="n"/>
@@ -2341,11 +2192,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
+          <t>Largest Loss (Rs)</t>
         </is>
       </c>
       <c r="B34" s="26" t="n">
-        <v>-322.94</v>
+        <v>-264.8</v>
       </c>
       <c r="C34" s="22" t="n"/>
       <c r="D34" s="23" t="n"/>
@@ -2353,11 +2204,11 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B35" s="30" t="n">
-        <v>-14.84</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="22" t="n"/>
       <c r="D35" s="23" t="n"/>
@@ -2365,11 +2216,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B36" s="25" t="n">
-        <v>-212.82</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="C36" s="22" t="n"/>
       <c r="D36" s="23" t="n"/>
@@ -2377,11 +2228,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
+          <t>Max trade drawdown (Rs)</t>
         </is>
       </c>
       <c r="B37" s="26" t="n">
-        <v>-358.86</v>
+        <v>-264.8</v>
       </c>
       <c r="C37" s="22" t="n"/>
       <c r="D37" s="23" t="n"/>
@@ -2389,11 +2240,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B38" s="21" t="n">
-        <v>0</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n">
+        <v>-1162.41</v>
       </c>
       <c r="C38" s="22" t="n"/>
       <c r="D38" s="23" t="n"/>
@@ -2401,11 +2252,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B39" s="21" t="n">
-        <v>5</v>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="n">
+        <v>-5.81</v>
       </c>
       <c r="C39" s="22" t="n"/>
       <c r="D39" s="23" t="n"/>
@@ -2413,11 +2264,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B40" s="26" t="n">
-        <v>-358.86</v>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="n">
+        <v>-1</v>
       </c>
       <c r="C40" s="22" t="n"/>
       <c r="D40" s="23" t="n"/>
@@ -2425,11 +2276,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B41" s="26" t="n">
-        <v>-1614.72</v>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="22" t="n"/>
       <c r="D41" s="23" t="n"/>
@@ -2437,11 +2288,13 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B42" s="30" t="n">
-        <v>-8.07</v>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="23" t="n"/>
@@ -2449,55 +2302,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Recovery Factor</t>
+          <t>Sharpe Ratio (annualized)</t>
         </is>
       </c>
       <c r="B43" s="31" t="n">
-        <v>-1</v>
+        <v>-46.07</v>
       </c>
       <c r="C43" s="22" t="n"/>
       <c r="D43" s="23" t="n"/>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B44" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="23" t="n"/>
-    </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="23" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B46" s="31" t="n">
-        <v>-36.94</v>
-      </c>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="23" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -2507,7 +2322,6 @@
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
@@ -2516,17 +2330,18 @@
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
   </mergeCells>
@@ -2541,7 +2356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2564,7 +2379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FINNIFTY -- best: trend_scalp_nw (EMA8/21) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>FINNIFTY -- best: trend_scalp_nw (EMA9/21) [1m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2469,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="4" t="n"/>
@@ -2662,359 +2477,320 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
+      <c r="H5" s="14" t="n">
+        <v>-0.027176</v>
+      </c>
       <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="14" t="n">
-        <v>-0.0136185</v>
-      </c>
+      <c r="J5" s="14" t="n">
+        <v>-0.04068053419734711</v>
+      </c>
+      <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="14" t="n">
-        <v>-0.02744830473807548</v>
-      </c>
-      <c r="N5" s="15" t="n">
-        <v>-0.04069299999999998</v>
-      </c>
-      <c r="O5" s="16" t="n">
-        <v>-813.86</v>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="17" t="n">
+        <v>-0.06675099999999989</v>
+      </c>
+      <c r="O5" s="20" t="n">
+        <v>-1335.02</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>-0.01495923619863089</v>
-      </c>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
+      <c r="H6" s="17" t="n">
+        <v>-0.027176</v>
+      </c>
       <c r="I6" s="4" t="n"/>
-      <c r="J6" s="14" t="n">
-        <v>-0.01223918772980555</v>
+      <c r="J6" s="17" t="n">
+        <v>-0.04068053419734711</v>
       </c>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="15" t="n">
-        <v>-0.027015335028307</v>
-      </c>
-      <c r="O6" s="16" t="n">
-        <v>-518.3200000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="n">
-        <v>-0.01495923619863089</v>
-      </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="15" t="n">
-        <v>-0.01223918772980555</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>-0.0136185</v>
-      </c>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="15" t="n">
-        <v>-0.02744830473807548</v>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jul</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>-0.027176</v>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="19" t="n">
+        <v>-0.027176</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>-543.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2025-Oct</t>
+          <t>2026-Sep</t>
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>-0.0136185</v>
-      </c>
-      <c r="C11" s="4" t="n"/>
+        <v>-0.0163390294647336</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>-0.02474582753788421</v>
+      </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="20" t="n">
-        <v>-0.0136185</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>-272.37</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2025-Dec</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="n">
-        <v>-0.02744830473807548</v>
-      </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="20" t="n">
-        <v>-0.02744830473807548</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>-541.49</v>
+      <c r="H11" s="19" t="n">
+        <v>-0.04068053419734711</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>-791.5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jan</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>-0.01495923619863089</v>
-      </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="20" t="n">
-        <v>-0.01495923619863089</v>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>-287.01</v>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>-0.01223918772980555</v>
-      </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="20" t="n">
-        <v>-0.01223918772980555</v>
-      </c>
-      <c r="I14" s="16" t="n">
-        <v>-231.31</v>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>13-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="14" t="n">
+        <v>-0.027176</v>
+      </c>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="19" t="n">
+        <v>-0.027176</v>
+      </c>
+      <c r="H15" s="20" t="n">
+        <v>-543.52</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="14" t="n">
+        <v>-0.0163390294647336</v>
+      </c>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="19" t="n">
+        <v>-0.0163390294647336</v>
+      </c>
+      <c r="H16" s="20" t="n">
+        <v>-317.9</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>13-Oct-2025</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="14" t="n">
-        <v>-0.0136185</v>
-      </c>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="20" t="n">
-        <v>-0.0136185</v>
-      </c>
-      <c r="H18" s="16" t="n">
-        <v>-272.37</v>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>28-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="14" t="n">
+        <v>-0.02474582753788421</v>
+      </c>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="19" t="n">
+        <v>-0.02474582753788421</v>
+      </c>
+      <c r="H17" s="20" t="n">
+        <v>-473.6</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>08-Dec-2025</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="14" t="n">
-        <v>-0.02744830473807548</v>
-      </c>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="20" t="n">
-        <v>-0.02744830473807548</v>
-      </c>
-      <c r="H19" s="16" t="n">
-        <v>-541.49</v>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="14" t="n">
-        <v>-0.01495923619863089</v>
-      </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="20" t="n">
-        <v>-0.01495923619863089</v>
-      </c>
-      <c r="H20" s="16" t="n">
-        <v>-287.01</v>
-      </c>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="23" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="14" t="n">
-        <v>-0.01223918772980555</v>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="20" t="n">
-        <v>-0.01223918772980555</v>
-      </c>
-      <c r="H21" s="16" t="n">
-        <v>-231.31</v>
-      </c>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="23" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>5 (100.0%)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="23" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="n">
+        <v>-1335.02</v>
+      </c>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="23" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="n">
-        <v>5</v>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="C24" s="22" t="n"/>
       <c r="D24" s="23" t="n"/>
@@ -3022,13 +2798,11 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="n">
+        <v>-1335.02</v>
       </c>
       <c r="C25" s="22" t="n"/>
       <c r="D25" s="23" t="n"/>
@@ -3036,13 +2810,11 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>5 (100.0%)</t>
-        </is>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="n">
+        <v>271.02</v>
       </c>
       <c r="C26" s="22" t="n"/>
       <c r="D26" s="23" t="n"/>
@@ -3050,11 +2822,11 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
+          <t>Avg Profit/Loss per trade (Rs)</t>
         </is>
       </c>
       <c r="B27" s="26" t="n">
-        <v>-1332.18</v>
+        <v>-267</v>
       </c>
       <c r="C27" s="22" t="n"/>
       <c r="D27" s="23" t="n"/>
@@ -3062,11 +2834,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B28" s="25" t="n">
-        <v>0</v>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="n">
+        <v>-14.84</v>
       </c>
       <c r="C28" s="22" t="n"/>
       <c r="D28" s="23" t="n"/>
@@ -3074,11 +2846,11 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="n">
-        <v>-1332.18</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="C29" s="22" t="n"/>
       <c r="D29" s="23" t="n"/>
@@ -3086,11 +2858,11 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B30" s="27" t="n">
-        <v>271.38</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B30" s="29" t="n">
+        <v>0</v>
       </c>
       <c r="C30" s="22" t="n"/>
       <c r="D30" s="23" t="n"/>
@@ -3098,11 +2870,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
+          <t>Avg Loss (Rs)</t>
         </is>
       </c>
       <c r="B31" s="26" t="n">
-        <v>-266.44</v>
+        <v>-267</v>
       </c>
       <c r="C31" s="22" t="n"/>
       <c r="D31" s="23" t="n"/>
@@ -3110,11 +2882,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B32" s="28" t="n">
-        <v>-14.85</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="n">
+        <v>-14.84</v>
       </c>
       <c r="C32" s="22" t="n"/>
       <c r="D32" s="23" t="n"/>
@@ -3122,11 +2894,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
+          <t>Largest Win (Rs)</t>
         </is>
       </c>
       <c r="B33" s="25" t="n">
-        <v>0</v>
+        <v>-216.68</v>
       </c>
       <c r="C33" s="22" t="n"/>
       <c r="D33" s="23" t="n"/>
@@ -3134,11 +2906,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B34" s="29" t="n">
-        <v>0</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>-317.9</v>
       </c>
       <c r="C34" s="22" t="n"/>
       <c r="D34" s="23" t="n"/>
@@ -3146,11 +2918,11 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B35" s="26" t="n">
-        <v>-266.44</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="22" t="n"/>
       <c r="D35" s="23" t="n"/>
@@ -3158,11 +2930,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B36" s="30" t="n">
-        <v>-14.85</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="C36" s="22" t="n"/>
       <c r="D36" s="23" t="n"/>
@@ -3170,11 +2942,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B37" s="25" t="n">
-        <v>-231.31</v>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n">
+        <v>-317.9</v>
       </c>
       <c r="C37" s="22" t="n"/>
       <c r="D37" s="23" t="n"/>
@@ -3182,11 +2954,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
+          <t>Max system drawdown (Rs)</t>
         </is>
       </c>
       <c r="B38" s="26" t="n">
-        <v>-295.95</v>
+        <v>-1335.02</v>
       </c>
       <c r="C38" s="22" t="n"/>
       <c r="D38" s="23" t="n"/>
@@ -3194,11 +2966,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B39" s="21" t="n">
-        <v>0</v>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="n">
+        <v>-6.68</v>
       </c>
       <c r="C39" s="22" t="n"/>
       <c r="D39" s="23" t="n"/>
@@ -3206,11 +2978,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B40" s="21" t="n">
-        <v>5</v>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="n">
+        <v>-1</v>
       </c>
       <c r="C40" s="22" t="n"/>
       <c r="D40" s="23" t="n"/>
@@ -3218,11 +2990,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B41" s="26" t="n">
-        <v>-295.95</v>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="22" t="n"/>
       <c r="D41" s="23" t="n"/>
@@ -3230,11 +3002,13 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B42" s="26" t="n">
-        <v>-1332.18</v>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="23" t="n"/>
@@ -3242,67 +3016,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B43" s="30" t="n">
-        <v>-6.66</v>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="n">
+        <v>-77.79000000000001</v>
       </c>
       <c r="C43" s="22" t="n"/>
       <c r="D43" s="23" t="n"/>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B44" s="31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="23" t="n"/>
-    </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B45" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="23" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="23" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B47" s="31" t="n">
-        <v>-44.63</v>
-      </c>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="23" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -3311,7 +3035,7 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
@@ -3320,18 +3044,18 @@
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B47:D47"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
   </mergeCells>
@@ -3346,7 +3070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3459,706 +3183,611 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="4" t="n"/>
+        <v>2026</v>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>0.007486499999999999</v>
+      </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
+      <c r="E5" s="13" t="n">
+        <v>0.007542532827983304</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>0.05840394725370424</v>
+      </c>
       <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
+      <c r="H5" s="14" t="n">
+        <v>-0.07320193545895015</v>
+      </c>
       <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="13" t="n">
-        <v>0.001868000000000001</v>
-      </c>
-      <c r="L5" s="14" t="n">
-        <v>-0.01919514347199431</v>
-      </c>
-      <c r="M5" s="14" t="n">
-        <v>-0.06368475846116115</v>
-      </c>
-      <c r="N5" s="15" t="n">
-        <v>-0.07994200000000007</v>
-      </c>
-      <c r="O5" s="16" t="n">
-        <v>-1598.84</v>
+      <c r="J5" s="14" t="n">
+        <v>-0.08522889614546995</v>
+      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="17" t="n">
+        <v>-0.08914000000000022</v>
+      </c>
+      <c r="O5" s="20" t="n">
+        <v>-1782.8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>-0.03431848861702198</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>0.02423287783784272</v>
-      </c>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="14" t="n">
-        <v>-0.01347122872352993</v>
-      </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="13" t="n">
-        <v>0.03094387162637448</v>
-      </c>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="14" t="n">
-        <v>-0.05060049085150257</v>
-      </c>
-      <c r="J6" s="14" t="n">
-        <v>-0.01316202762711363</v>
+      <c r="E6" s="15" t="n">
+        <v>0.007542532827983304</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>0.05840394725370424</v>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="17" t="n">
+        <v>-0.07320193545895015</v>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="17" t="n">
+        <v>-0.08522889614546995</v>
       </c>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="15" t="n">
-        <v>-0.05751974332052978</v>
-      </c>
-      <c r="O6" s="16" t="n">
-        <v>-1058.43</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="n">
-        <v>-0.03431848861702198</v>
-      </c>
-      <c r="C7" s="17" t="n">
-        <v>0.02423287783784272</v>
-      </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="15" t="n">
-        <v>-0.01347122872352993</v>
-      </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="17" t="n">
-        <v>0.03094387162637448</v>
-      </c>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="15" t="n">
-        <v>-0.05060049085150257</v>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>-0.01316202762711363</v>
-      </c>
-      <c r="K7" s="17" t="n">
-        <v>0.001868000000000001</v>
-      </c>
-      <c r="L7" s="15" t="n">
-        <v>-0.01919514347199431</v>
-      </c>
-      <c r="M7" s="15" t="n">
-        <v>-0.06368475846116115</v>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jan</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="18" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>149.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2025-Oct</t>
+          <t>2026-Apr</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>0.0154865</v>
+        <v>0.02240377414486447</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>-0.0134108134376971</v>
+        <v>-0.01453558925808061</v>
       </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="19" t="n">
-        <v>0.001868000000000001</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>37.36</v>
+      <c r="H11" s="18" t="n">
+        <v>0.007542532827983304</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>151.98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2025-Nov</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="n">
-        <v>-0.01630703845217134</v>
-      </c>
-      <c r="C12" s="14" t="n">
-        <v>-0.002935982194361311</v>
-      </c>
+          <t>2026-May</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>0.05840394725370424</v>
+      </c>
+      <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="20" t="n">
-        <v>-0.01919514347199431</v>
+      <c r="H12" s="18" t="n">
+        <v>0.05840394725370424</v>
       </c>
       <c r="I12" s="16" t="n">
-        <v>-384.62</v>
+        <v>1185.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2025-Dec</t>
+          <t>2026-Jul</t>
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>-0.02755290102041751</v>
+        <v>-0.01546998917040258</v>
       </c>
       <c r="C13" s="14" t="n">
-        <v>-0.03715560206684546</v>
-      </c>
-      <c r="D13" s="4" t="n"/>
+        <v>-0.04929992909477665</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>-0.009823459158335844</v>
+      </c>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
-      <c r="H13" s="20" t="n">
-        <v>-0.06368475846116115</v>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>-1251.58</v>
+      <c r="H13" s="19" t="n">
+        <v>-0.07320193545895015</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>-1572.92</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-Jan</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>0.01397574935493198</v>
+          <t>2026-Sep</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>-0.02881419509111205</v>
       </c>
       <c r="C14" s="14" t="n">
-        <v>-0.04762859269827473</v>
-      </c>
-      <c r="D14" s="4" t="n"/>
+        <v>-0.009536898152959539</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>-0.0490190653479653</v>
+      </c>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
-      <c r="H14" s="20" t="n">
-        <v>-0.03431848861702198</v>
-      </c>
-      <c r="I14" s="16" t="n">
-        <v>-631.5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2026-Feb</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>0.02423287783784272</v>
-      </c>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="19" t="n">
-        <v>0.02423287783784272</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>430.61</v>
+      <c r="H14" s="19" t="n">
+        <v>-0.08522889614546995</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>-1697.29</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2026-Apr</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>-0.01347122872352993</v>
-      </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="20" t="n">
-        <v>-0.01347122872352993</v>
-      </c>
-      <c r="I16" s="16" t="n">
-        <v>-245.18</v>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jun</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>0.01436417194232945</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>0.01634491846483281</v>
-      </c>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="19" t="n">
-        <v>0.03094387162637448</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>555.6</v>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-Aug</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n">
-        <v>-0.03910335055041169</v>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>-0.01196501237430328</v>
+          <t>19-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="13" t="n">
+        <v>0.007486499999999999</v>
       </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="20" t="n">
-        <v>-0.05060049085150257</v>
-      </c>
-      <c r="I18" s="16" t="n">
-        <v>-936.65</v>
+      <c r="G18" s="18" t="n">
+        <v>0.007486499999999999</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>149.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="n">
-        <v>-0.01316202762711363</v>
-      </c>
-      <c r="C19" s="4" t="n"/>
+          <t>06-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="13" t="n">
+        <v>0.02240377414486447</v>
+      </c>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="20" t="n">
-        <v>-0.01316202762711363</v>
-      </c>
-      <c r="I19" s="16" t="n">
-        <v>-231.31</v>
+      <c r="G19" s="18" t="n">
+        <v>0.02240377414486447</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>451.43</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="14" t="n">
+        <v>-0.01453558925808061</v>
+      </c>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="19" t="n">
+        <v>-0.01453558925808061</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>-299.45</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="13" t="n">
+        <v>0.05840394725370424</v>
+      </c>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="18" t="n">
+        <v>0.05840394725370424</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>1185.7</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>06-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="14" t="n">
+        <v>-0.01546998917040258</v>
+      </c>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="19" t="n">
+        <v>-0.01546998917040258</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>-332.41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>06-Oct-2025</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="C23" s="4" t="n"/>
+          <t>13-Jul-2026</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="14" t="n">
+        <v>-0.04929992909477665</v>
+      </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
       <c r="G23" s="19" t="n">
-        <v>0.0154865</v>
-      </c>
-      <c r="H23" s="18" t="n">
-        <v>309.73</v>
+        <v>-0.04929992909477665</v>
+      </c>
+      <c r="H23" s="20" t="n">
+        <v>-1042.94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>13-Oct-2025</t>
+          <t>27-Jul-2026</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
       <c r="C24" s="14" t="n">
-        <v>-0.0134108134376971</v>
+        <v>-0.009823459158335844</v>
       </c>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
-      <c r="G24" s="20" t="n">
-        <v>-0.0134108134376971</v>
-      </c>
-      <c r="H24" s="16" t="n">
-        <v>-272.37</v>
+      <c r="G24" s="19" t="n">
+        <v>-0.009823459158335844</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <v>-197.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>10-Nov-2025</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
       <c r="C25" s="14" t="n">
-        <v>-0.01630703845217134</v>
+        <v>-0.02881419509111205</v>
       </c>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
-      <c r="G25" s="20" t="n">
-        <v>-0.01630703845217134</v>
-      </c>
-      <c r="H25" s="16" t="n">
-        <v>-326.75</v>
+      <c r="G25" s="19" t="n">
+        <v>-0.02881419509111205</v>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>-573.8200000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>24-Nov-2025</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="n">
-        <v>0.01547187022623856</v>
-      </c>
+          <t>14-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
       <c r="C26" s="14" t="n">
-        <v>-0.01812738782857545</v>
+        <v>-0.009536898152959539</v>
       </c>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
-      <c r="G26" s="20" t="n">
-        <v>-0.002935982194361311</v>
-      </c>
-      <c r="H26" s="16" t="n">
-        <v>-57.87</v>
+      <c r="G26" s="19" t="n">
+        <v>-0.009536898152959539</v>
+      </c>
+      <c r="H26" s="20" t="n">
+        <v>-184.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>08-Dec-2025</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
       <c r="C27" s="14" t="n">
-        <v>-0.02755290102041751</v>
+        <v>-0.0490190653479653</v>
       </c>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
-      <c r="G27" s="20" t="n">
-        <v>-0.02755290102041751</v>
-      </c>
-      <c r="H27" s="16" t="n">
-        <v>-541.49</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>29-Dec-2025</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="14" t="n">
-        <v>-0.03715560206684546</v>
-      </c>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="20" t="n">
-        <v>-0.03715560206684546</v>
-      </c>
-      <c r="H28" s="16" t="n">
-        <v>-710.09</v>
+      <c r="G27" s="19" t="n">
+        <v>-0.0490190653479653</v>
+      </c>
+      <c r="H27" s="20" t="n">
+        <v>-939.02</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>12-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="n">
-        <v>0.01397574935493198</v>
-      </c>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="19" t="n">
-        <v>0.01397574935493198</v>
-      </c>
-      <c r="H29" s="18" t="n">
-        <v>257.17</v>
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="14" t="n">
-        <v>-0.04762859269827473</v>
-      </c>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="20" t="n">
-        <v>-0.02454989272887767</v>
-      </c>
-      <c r="H30" s="16" t="n">
-        <v>-458.06</v>
-      </c>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="23" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="n">
-        <v>-0.01347122872352993</v>
-      </c>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="20" t="n">
-        <v>-0.01347122872352993</v>
-      </c>
-      <c r="H31" s="16" t="n">
-        <v>-245.18</v>
-      </c>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>5 (22.7%)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="23" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="n">
-        <v>0.01436417194232945</v>
-      </c>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="19" t="n">
-        <v>0.01436417194232945</v>
-      </c>
-      <c r="H32" s="18" t="n">
-        <v>257.91</v>
-      </c>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>17 (77.3%)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="23" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="n">
-        <v>0.01634491846483281</v>
-      </c>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="19" t="n">
-        <v>0.01634491846483281</v>
-      </c>
-      <c r="H33" s="18" t="n">
-        <v>297.69</v>
-      </c>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n">
+        <v>-1782.8</v>
+      </c>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="23" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>10-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="14" t="n">
-        <v>-0.03910335055041169</v>
-      </c>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="20" t="n">
-        <v>-0.03910335055041169</v>
-      </c>
-      <c r="H34" s="16" t="n">
-        <v>-723.83</v>
-      </c>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="n">
+        <v>2338.58</v>
+      </c>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="23" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>24-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="14" t="n">
-        <v>-0.01196501237430328</v>
-      </c>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="20" t="n">
-        <v>-0.01196501237430328</v>
-      </c>
-      <c r="H35" s="16" t="n">
-        <v>-212.82</v>
-      </c>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n">
+        <v>-4121.38</v>
+      </c>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="23" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="14" t="n">
-        <v>-0.01316202762711363</v>
-      </c>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="20" t="n">
-        <v>-0.01316202762711363</v>
-      </c>
-      <c r="H36" s="16" t="n">
-        <v>-231.31</v>
-      </c>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="n">
+        <v>842.95</v>
+      </c>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="23" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n">
+        <v>-81.04000000000001</v>
+      </c>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="23" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B38" s="28" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="23" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B39" s="21" t="n">
-        <v>23</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="n">
+        <v>467.72</v>
       </c>
       <c r="C39" s="22" t="n"/>
       <c r="D39" s="23" t="n"/>
@@ -4166,13 +3795,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>7 (30.4%)</t>
-        </is>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B40" s="29" t="n">
+        <v>54.93</v>
       </c>
       <c r="C40" s="22" t="n"/>
       <c r="D40" s="23" t="n"/>
@@ -4180,13 +3807,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>16 (69.6%)</t>
-        </is>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="n">
+        <v>-242.43</v>
       </c>
       <c r="C41" s="22" t="n"/>
       <c r="D41" s="23" t="n"/>
@@ -4194,11 +3819,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B42" s="26" t="n">
-        <v>-2657.27</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B42" s="30" t="n">
+        <v>-20.76</v>
       </c>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="23" t="n"/>
@@ -4206,11 +3831,11 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
+          <t>Largest Win (Rs)</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
-        <v>2174.65</v>
+        <v>552.97</v>
       </c>
       <c r="C43" s="22" t="n"/>
       <c r="D43" s="23" t="n"/>
@@ -4218,11 +3843,11 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
+          <t>Largest Loss (Rs)</t>
         </is>
       </c>
       <c r="B44" s="26" t="n">
-        <v>-4831.92</v>
+        <v>-332.41</v>
       </c>
       <c r="C44" s="22" t="n"/>
       <c r="D44" s="23" t="n"/>
@@ -4230,11 +3855,11 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B45" s="27" t="n">
-        <v>1462.97</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="C45" s="22" t="n"/>
       <c r="D45" s="23" t="n"/>
@@ -4242,11 +3867,11 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B46" s="26" t="n">
-        <v>-115.53</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="n">
+        <v>14</v>
       </c>
       <c r="C46" s="22" t="n"/>
       <c r="D46" s="23" t="n"/>
@@ -4254,11 +3879,11 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B47" s="28" t="n">
-        <v>-5.45</v>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="n">
+        <v>-332.41</v>
       </c>
       <c r="C47" s="22" t="n"/>
       <c r="D47" s="23" t="n"/>
@@ -4266,11 +3891,11 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="n">
-        <v>310.66</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B48" s="26" t="n">
+        <v>-3501.72</v>
       </c>
       <c r="C48" s="22" t="n"/>
       <c r="D48" s="23" t="n"/>
@@ -4278,11 +3903,11 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B49" s="29" t="n">
-        <v>16.01</v>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B49" s="30" t="n">
+        <v>-16.12</v>
       </c>
       <c r="C49" s="22" t="n"/>
       <c r="D49" s="23" t="n"/>
@@ -4290,11 +3915,11 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B50" s="26" t="n">
-        <v>-302</v>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B50" s="31" t="n">
+        <v>-0.51</v>
       </c>
       <c r="C50" s="22" t="n"/>
       <c r="D50" s="23" t="n"/>
@@ -4302,11 +3927,11 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B51" s="30" t="n">
-        <v>-14.84</v>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="n">
+        <v>0.57</v>
       </c>
       <c r="C51" s="22" t="n"/>
       <c r="D51" s="23" t="n"/>
@@ -4314,11 +3939,11 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B52" s="25" t="n">
-        <v>406.75</v>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B52" s="31" t="n">
+        <v>1.93</v>
       </c>
       <c r="C52" s="22" t="n"/>
       <c r="D52" s="23" t="n"/>
@@ -4326,125 +3951,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B53" s="26" t="n">
-        <v>-368.93</v>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B53" s="31" t="n">
+        <v>-4.54</v>
       </c>
       <c r="C53" s="22" t="n"/>
       <c r="D53" s="23" t="n"/>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B54" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" s="22" t="n"/>
-      <c r="D54" s="23" t="n"/>
-    </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B55" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="C55" s="22" t="n"/>
-      <c r="D55" s="23" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B56" s="26" t="n">
-        <v>-368.93</v>
-      </c>
-      <c r="C56" s="22" t="n"/>
-      <c r="D56" s="23" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B57" s="26" t="n">
-        <v>-3321.99</v>
-      </c>
-      <c r="C57" s="22" t="n"/>
-      <c r="D57" s="23" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B58" s="30" t="n">
-        <v>-16.08</v>
-      </c>
-      <c r="C58" s="22" t="n"/>
-      <c r="D58" s="23" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B59" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="C59" s="22" t="n"/>
-      <c r="D59" s="23" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B60" s="31" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C60" s="22" t="n"/>
-      <c r="D60" s="23" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B61" s="31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="C61" s="22" t="n"/>
-      <c r="D61" s="23" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B62" s="31" t="n">
-        <v>-6.22</v>
-      </c>
-      <c r="C62" s="22" t="n"/>
-      <c r="D62" s="23" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="11" t="inlineStr">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -4453,25 +3970,25 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B57:D57"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B37:D37"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B36:D36"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B62:D62"/>
     <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>

--- a/reports/latest_backtest_dashboard.xlsx
+++ b/reports/latest_backtest_dashboard.xlsx
@@ -68,12 +68,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="000B8A00"/>
+      <color rgb="00C00000"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="000B8A00"/>
     </font>
   </fonts>
   <fills count="5">
@@ -91,14 +91,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
-        <bgColor rgb="00E6F4EA"/>
+        <fgColor rgb="00FDE8E8"/>
+        <bgColor rgb="00FDE8E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDE8E8"/>
-        <bgColor rgb="00FDE8E8"/>
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -188,14 +188,14 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -654,23 +654,23 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum (EMA9/13) [60m]</t>
+          <t>vwap_ema_momentum (EMA9/13) [5m]</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>714.63</v>
+        <v>277.15</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>-0.04624032870879385</v>
+        <v>-0.01480658481386824</v>
       </c>
     </row>
     <row r="5">
@@ -681,23 +681,23 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>trend_scalp_nw (EMA5/21) [1m]</t>
+          <t>trend_scalp_nw (EMA5/21) [5m]</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>-1162.41</v>
+        <v>-1792.63</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>-0.05812049999999982</v>
+        <v>-0.08963150000000004</v>
       </c>
     </row>
     <row r="6">
@@ -708,23 +708,23 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>trend_scalp_nw (EMA9/21) [1m]</t>
+          <t>trend_scalp_nw (EMA9/26) [5m]</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>-1335.02</v>
+        <v>-1219.59</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>-0.06675100000000002</v>
+        <v>-0.06126299999999993</v>
       </c>
     </row>
     <row r="7">
@@ -739,19 +739,19 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>-1782.8</v>
+        <v>-2735.07</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.57</v>
+        <v>0.32</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.1612290113873062</v>
+        <v>-0.1569609630790708</v>
       </c>
     </row>
     <row r="9">
@@ -773,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -796,7 +796,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NIFTY -- best: vwap_ema_momentum (EMA9/13) [60m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>NIFTY -- best: vwap_ema_momentum (EMA9/13) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
@@ -888,33 +888,29 @@
       <c r="A5" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="B5" s="13" t="n">
-        <v>0.007486499999999999</v>
-      </c>
+      <c r="B5" s="4" t="n"/>
       <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="13" t="n">
-        <v>0.007542532827983304</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>0.05840394725370424</v>
+      <c r="D5" s="13" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="14" t="n">
+        <v>0.02750410797474085</v>
       </c>
       <c r="G5" s="4" t="n"/>
-      <c r="H5" s="14" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
+      <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
-      <c r="J5" s="14" t="n">
-        <v>-0.02081635547151973</v>
-      </c>
-      <c r="K5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="13" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="15" t="n">
-        <v>0.03573149999999981</v>
+        <v>0.01385750000000008</v>
       </c>
       <c r="O5" s="16" t="n">
-        <v>714.63</v>
+        <v>277.15</v>
       </c>
     </row>
     <row r="6">
@@ -923,26 +919,22 @@
           <t>Avg</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
-        <v>0.007486499999999999</v>
-      </c>
+      <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="15" t="n">
-        <v>0.007542532827983304</v>
-      </c>
+      <c r="D6" s="17" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="E6" s="4" t="n"/>
       <c r="F6" s="15" t="n">
-        <v>0.05840394725370424</v>
+        <v>0.02750410797474085</v>
       </c>
       <c r="G6" s="4" t="n"/>
-      <c r="H6" s="17" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
+      <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
-      <c r="J6" s="17" t="n">
-        <v>-0.02081635547151973</v>
-      </c>
-      <c r="K6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="17" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
     </row>
@@ -1003,11 +995,11 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-Jan</t>
+          <t>2026-Mar</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>0.007486499999999999</v>
+        <v>-0.003766999999999999</v>
       </c>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
@@ -1015,43 +1007,41 @@
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="18" t="n">
-        <v>0.007486499999999999</v>
-      </c>
-      <c r="I10" s="16" t="n">
-        <v>149.73</v>
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>-75.34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-Apr</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="n">
-        <v>0.02240377414486447</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>-0.01453558925808061</v>
-      </c>
+          <t>2026-May</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="18" t="n">
-        <v>0.007542532827983304</v>
+      <c r="H11" s="20" t="n">
+        <v>0.02750410797474085</v>
       </c>
       <c r="I11" s="16" t="n">
-        <v>151.98</v>
+        <v>548.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-May</t>
+          <t>2026-Oct</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>0.05840394725370424</v>
+        <v>-0.009550293146912445</v>
       </c>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
@@ -1059,260 +1049,212 @@
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="18" t="n">
-        <v>0.05840394725370424</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>1185.7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jul</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="19" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <v>-332.41</v>
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>-195.52</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>-0.012097376506736</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>-0.008825747353472017</v>
-      </c>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="19" t="n">
-        <v>-0.02081635547151973</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>-440.37</v>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>23-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="13" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="18" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>-75.34</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="14" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="20" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>548.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>19-Jan-2026</t>
+          <t>12-Oct-2026</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
       <c r="C18" s="13" t="n">
-        <v>0.007486499999999999</v>
+        <v>-0.009550293146912445</v>
       </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="18" t="n">
-        <v>0.007486499999999999</v>
-      </c>
-      <c r="H18" s="16" t="n">
-        <v>149.73</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>06-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="13" t="n">
-        <v>0.02240377414486447</v>
-      </c>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="18" t="n">
-        <v>0.02240377414486447</v>
-      </c>
-      <c r="H19" s="16" t="n">
-        <v>451.43</v>
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>-195.52</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>20-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="14" t="n">
-        <v>-0.01453558925808061</v>
-      </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="19" t="n">
-        <v>-0.01453558925808061</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>-299.45</v>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="13" t="n">
-        <v>0.05840394725370424</v>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="18" t="n">
-        <v>0.05840394725370424</v>
-      </c>
-      <c r="H21" s="16" t="n">
-        <v>1185.7</v>
-      </c>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="23" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>06-Jul-2026</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="14" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="19" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <v>-332.41</v>
-      </c>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2 (40.0%)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="23" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="14" t="n">
-        <v>-0.012097376506736</v>
-      </c>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="19" t="n">
-        <v>-0.012097376506736</v>
-      </c>
-      <c r="H23" s="20" t="n">
-        <v>-255.92</v>
-      </c>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>3 (60.0%)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="23" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>14-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="14" t="n">
-        <v>-0.008825747353472017</v>
-      </c>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="19" t="n">
-        <v>-0.008825747353472017</v>
-      </c>
-      <c r="H24" s="20" t="n">
-        <v>-184.45</v>
-      </c>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="23" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>1040.37</v>
+      </c>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="23" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n">
+        <v>-763.22</v>
+      </c>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="23" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="n">
-        <v>12</v>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="n">
+        <v>143.6</v>
       </c>
       <c r="C27" s="22" t="n"/>
       <c r="D27" s="23" t="n"/>
@@ -1320,13 +1262,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>5 (41.7%)</t>
-        </is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="n">
+        <v>55.43</v>
       </c>
       <c r="C28" s="22" t="n"/>
       <c r="D28" s="23" t="n"/>
@@ -1334,13 +1274,11 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>7 (58.3%)</t>
-        </is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="n">
+        <v>2.6</v>
       </c>
       <c r="C29" s="22" t="n"/>
       <c r="D29" s="23" t="n"/>
@@ -1348,11 +1286,11 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
+          <t>Avg Win (Rs)</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
-        <v>714.63</v>
+        <v>520.1799999999999</v>
       </c>
       <c r="C30" s="22" t="n"/>
       <c r="D30" s="23" t="n"/>
@@ -1360,11 +1298,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="n">
-        <v>2338.58</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="n">
+        <v>54.92</v>
       </c>
       <c r="C31" s="22" t="n"/>
       <c r="D31" s="23" t="n"/>
@@ -1372,11 +1310,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
+          <t>Avg Loss (Rs)</t>
         </is>
       </c>
       <c r="B32" s="26" t="n">
-        <v>-1623.95</v>
+        <v>-254.41</v>
       </c>
       <c r="C32" s="22" t="n"/>
       <c r="D32" s="23" t="n"/>
@@ -1384,11 +1322,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="n">
-        <v>335.62</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="n">
+        <v>-32.27</v>
       </c>
       <c r="C33" s="22" t="n"/>
       <c r="D33" s="23" t="n"/>
@@ -1396,11 +1334,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
+          <t>Largest Win (Rs)</t>
         </is>
       </c>
       <c r="B34" s="25" t="n">
-        <v>59.55</v>
+        <v>548.01</v>
       </c>
       <c r="C34" s="22" t="n"/>
       <c r="D34" s="23" t="n"/>
@@ -1408,11 +1346,11 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B35" s="28" t="n">
-        <v>5.84</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n">
+        <v>-299.45</v>
       </c>
       <c r="C35" s="22" t="n"/>
       <c r="D35" s="23" t="n"/>
@@ -1420,11 +1358,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B36" s="25" t="n">
-        <v>467.72</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="C36" s="22" t="n"/>
       <c r="D36" s="23" t="n"/>
@@ -1432,11 +1370,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B37" s="29" t="n">
-        <v>54.93</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="C37" s="22" t="n"/>
       <c r="D37" s="23" t="n"/>
@@ -1444,11 +1382,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
+          <t>Max trade drawdown (Rs)</t>
         </is>
       </c>
       <c r="B38" s="26" t="n">
-        <v>-231.99</v>
+        <v>-299.45</v>
       </c>
       <c r="C38" s="22" t="n"/>
       <c r="D38" s="23" t="n"/>
@@ -1456,11 +1394,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B39" s="30" t="n">
-        <v>-29.23</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n">
+        <v>-299.45</v>
       </c>
       <c r="C39" s="22" t="n"/>
       <c r="D39" s="23" t="n"/>
@@ -1468,11 +1406,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B40" s="25" t="n">
-        <v>552.97</v>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="n">
+        <v>-1.48</v>
       </c>
       <c r="C40" s="22" t="n"/>
       <c r="D40" s="23" t="n"/>
@@ -1480,11 +1418,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B41" s="26" t="n">
-        <v>-332.41</v>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="n">
+        <v>0.93</v>
       </c>
       <c r="C41" s="22" t="n"/>
       <c r="D41" s="23" t="n"/>
@@ -1492,11 +1430,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B42" s="21" t="n">
-        <v>3</v>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B42" s="31" t="n">
+        <v>1.36</v>
       </c>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="23" t="n"/>
@@ -1504,11 +1442,11 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B43" s="21" t="n">
-        <v>4</v>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="n">
+        <v>2.04</v>
       </c>
       <c r="C43" s="22" t="n"/>
       <c r="D43" s="23" t="n"/>
@@ -1516,89 +1454,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B44" s="26" t="n">
-        <v>-332.41</v>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="n">
+        <v>4.61</v>
       </c>
       <c r="C44" s="22" t="n"/>
       <c r="D44" s="23" t="n"/>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B45" s="26" t="n">
-        <v>-1004.29</v>
-      </c>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="23" t="n"/>
-    </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B46" s="30" t="n">
-        <v>-4.62</v>
-      </c>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="23" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B47" s="31" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="23" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B48" s="31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="23" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B49" s="31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="C49" s="22" t="n"/>
-      <c r="D49" s="23" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B50" s="31" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="23" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -1607,29 +1473,29 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B23:D23"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1642,7 +1508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1665,7 +1531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANKNIFTY -- best: trend_scalp_nw (EMA5/21) [1m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>BANKNIFTY -- best: trend_scalp_nw (EMA5/21) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1621,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="4" t="n"/>
@@ -1763,332 +1629,381 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
-      <c r="H5" s="14" t="n">
-        <v>-0.0348495</v>
-      </c>
+      <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
-      <c r="J5" s="14" t="n">
-        <v>-0.02411126554874084</v>
-      </c>
+      <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
+      <c r="M5" s="13" t="n">
+        <v>-0.0355045</v>
+      </c>
       <c r="N5" s="17" t="n">
-        <v>-0.05812050000000002</v>
-      </c>
-      <c r="O5" s="20" t="n">
-        <v>-1162.41</v>
+        <v>-0.03550450000000005</v>
+      </c>
+      <c r="O5" s="19" t="n">
+        <v>-710.09</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n"/>
+      <c r="A6" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
-      <c r="H6" s="17" t="n">
-        <v>-0.0348495</v>
-      </c>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="17" t="n">
-        <v>-0.02411126554874084</v>
-      </c>
-      <c r="K6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="13" t="n">
+        <v>-0.02995409697673192</v>
+      </c>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="13" t="n">
+        <v>-0.009676763149650155</v>
+      </c>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="N6" s="17" t="n">
+        <v>-0.05611949459587939</v>
+      </c>
+      <c r="O6" s="19" t="n">
+        <v>-1082.54</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="17" t="n">
+        <v>-0.02995409697673192</v>
+      </c>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="17" t="n">
+        <v>-0.009676763149650155</v>
+      </c>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="17" t="n">
+        <v>-0.0355045</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Month %</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Month P&amp;L (Rs)</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jul</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n">
-        <v>-0.024971</v>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>-0.01013149352480798</v>
-      </c>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="19" t="n">
-        <v>-0.0348495</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>-696.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>-0.02411126554874084</v>
+          <t>2025-Dec</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>-0.0355045</v>
       </c>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="19" t="n">
-        <v>-0.02411126554874084</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>-465.42</v>
+      <c r="H11" s="18" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>-710.09</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jan</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="18" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>-336.91</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-Aug</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>-0.01872526776763573</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>-0.01144310440313796</v>
+      </c>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="18" t="n">
+        <v>-0.02995409697673192</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>-567.72</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-Oct</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>-0.009676763149650155</v>
+      </c>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="18" t="n">
+        <v>-0.009676763149650155</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>-177.91</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Week starting (Mon)</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Week %</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Week P&amp;L (Rs)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>13-Jul-2026</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="14" t="n">
-        <v>-0.024971</v>
-      </c>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="19" t="n">
-        <v>-0.024971</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>-499.42</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>27-Jul-2026</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="14" t="n">
-        <v>-0.01013149352480798</v>
-      </c>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="19" t="n">
-        <v>-0.01013149352480798</v>
-      </c>
-      <c r="H16" s="20" t="n">
-        <v>-197.57</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>28-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="14" t="n">
-        <v>-0.02411126554874084</v>
-      </c>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="19" t="n">
-        <v>-0.02411126554874084</v>
-      </c>
-      <c r="H17" s="20" t="n">
-        <v>-465.42</v>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>29-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="13" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="18" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>-710.09</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>26-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="13" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="18" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>-336.91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="23" t="n"/>
+          <t>10-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="13" t="n">
+        <v>-0.01872526776763573</v>
+      </c>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="18" t="n">
+        <v>-0.01872526776763573</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>-354.9</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="23" t="n"/>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="13" t="n">
+        <v>-0.01144310440313796</v>
+      </c>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="18" t="n">
+        <v>-0.01144310440313796</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>-212.82</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>5 (100.0%)</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="23" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B23" s="26" t="n">
-        <v>-1162.41</v>
-      </c>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="23" t="n"/>
+          <t>12-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="13" t="n">
+        <v>-0.009676763149650155</v>
+      </c>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="18" t="n">
+        <v>-0.009676763149650155</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>-177.91</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="23" t="n"/>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="n">
-        <v>-1162.41</v>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="C25" s="22" t="n"/>
       <c r="D25" s="23" t="n"/>
@@ -2096,11 +2011,13 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="n">
-        <v>236.31</v>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
       </c>
       <c r="C26" s="22" t="n"/>
       <c r="D26" s="23" t="n"/>
@@ -2108,11 +2025,13 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="n">
-        <v>-232.48</v>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>6 (100.0%)</t>
+        </is>
       </c>
       <c r="C27" s="22" t="n"/>
       <c r="D27" s="23" t="n"/>
@@ -2120,11 +2039,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B28" s="28" t="n">
-        <v>-14.84</v>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n">
+        <v>-1792.63</v>
       </c>
       <c r="C28" s="22" t="n"/>
       <c r="D28" s="23" t="n"/>
@@ -2132,7 +2051,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
+          <t>Total Profit (Rs)</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
@@ -2144,11 +2063,11 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B30" s="29" t="n">
-        <v>0</v>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n">
+        <v>-1792.63</v>
       </c>
       <c r="C30" s="22" t="n"/>
       <c r="D30" s="23" t="n"/>
@@ -2156,11 +2075,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="n">
-        <v>-232.48</v>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="n">
+        <v>364.63</v>
       </c>
       <c r="C31" s="22" t="n"/>
       <c r="D31" s="23" t="n"/>
@@ -2168,11 +2087,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B32" s="30" t="n">
-        <v>-14.84</v>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n">
+        <v>-298.77</v>
       </c>
       <c r="C32" s="22" t="n"/>
       <c r="D32" s="23" t="n"/>
@@ -2180,11 +2099,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="n">
-        <v>-197.57</v>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n">
+        <v>-14.84</v>
       </c>
       <c r="C33" s="22" t="n"/>
       <c r="D33" s="23" t="n"/>
@@ -2192,11 +2111,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="n">
-        <v>-264.8</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="C34" s="22" t="n"/>
       <c r="D34" s="23" t="n"/>
@@ -2204,10 +2123,10 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="n">
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="22" t="n"/>
@@ -2216,11 +2135,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="n">
-        <v>5</v>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n">
+        <v>-298.77</v>
       </c>
       <c r="C36" s="22" t="n"/>
       <c r="D36" s="23" t="n"/>
@@ -2228,11 +2147,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B37" s="26" t="n">
-        <v>-264.8</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="n">
+        <v>-14.84</v>
       </c>
       <c r="C37" s="22" t="n"/>
       <c r="D37" s="23" t="n"/>
@@ -2240,11 +2159,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="26" t="n">
-        <v>-1162.41</v>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="n">
+        <v>-177.91</v>
       </c>
       <c r="C38" s="22" t="n"/>
       <c r="D38" s="23" t="n"/>
@@ -2252,11 +2171,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B39" s="30" t="n">
-        <v>-5.81</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n">
+        <v>-358.86</v>
       </c>
       <c r="C39" s="22" t="n"/>
       <c r="D39" s="23" t="n"/>
@@ -2264,11 +2183,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B40" s="31" t="n">
-        <v>-1</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="22" t="n"/>
       <c r="D40" s="23" t="n"/>
@@ -2276,11 +2195,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B41" s="31" t="n">
-        <v>0</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="C41" s="22" t="n"/>
       <c r="D41" s="23" t="n"/>
@@ -2288,13 +2207,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="n">
+        <v>-358.86</v>
       </c>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="23" t="n"/>
@@ -2302,17 +2219,79 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B43" s="31" t="n">
-        <v>-46.07</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="n">
+        <v>-1792.63</v>
       </c>
       <c r="C43" s="22" t="n"/>
       <c r="D43" s="23" t="n"/>
     </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B44" s="30" t="n">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="23" t="n"/>
+    </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="23" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B46" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="23" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="23" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B48" s="31" t="n">
+        <v>-32.23</v>
+      </c>
+      <c r="C48" s="22" t="n"/>
+      <c r="D48" s="23" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -2321,7 +2300,7 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
@@ -2329,21 +2308,21 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B47:D47"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2356,7 +2335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2379,7 +2358,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FINNIFTY -- best: trend_scalp_nw (EMA9/21) [1m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>FINNIFTY -- best: trend_scalp_nw (EMA9/26) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2448,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="4" t="n"/>
@@ -2477,332 +2456,381 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
-      <c r="H5" s="14" t="n">
-        <v>-0.027176</v>
-      </c>
+      <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
-      <c r="J5" s="14" t="n">
-        <v>-0.04068053419734711</v>
-      </c>
+      <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
+      <c r="M5" s="13" t="n">
+        <v>-0.0469125</v>
+      </c>
       <c r="N5" s="17" t="n">
-        <v>-0.06675099999999989</v>
-      </c>
-      <c r="O5" s="20" t="n">
-        <v>-1335.02</v>
+        <v>-0.04691250000000002</v>
+      </c>
+      <c r="O5" s="19" t="n">
+        <v>-938.25</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n"/>
+      <c r="A6" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
+      <c r="E6" s="14" t="n">
+        <v>0.01262227865738753</v>
+      </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
-      <c r="H6" s="17" t="n">
-        <v>-0.027176</v>
-      </c>
+      <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
-      <c r="J6" s="17" t="n">
-        <v>-0.04068053419734711</v>
+      <c r="J6" s="13" t="n">
+        <v>-0.01216670559002552</v>
       </c>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="N6" s="17" t="n">
+        <v>-0.01475940036985068</v>
+      </c>
+      <c r="O6" s="19" t="n">
+        <v>-281.34</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="15" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="17" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="17" t="n">
+        <v>-0.0469125</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Month %</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Month P&amp;L (Rs)</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jul</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n">
-        <v>-0.027176</v>
-      </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="19" t="n">
-        <v>-0.027176</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>-543.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n">
-        <v>-0.0163390294647336</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>-0.02474582753788421</v>
+          <t>2025-Dec</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>-0.0369487719950609</v>
       </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="19" t="n">
-        <v>-0.04068053419734711</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>-791.5</v>
+      <c r="H11" s="18" t="n">
+        <v>-0.0469125</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>-938.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-Jan</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="18" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>-287.01</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-Apr</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="20" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>236.98</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-Sep</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="18" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="I14" s="19" t="n">
+        <v>-231.31</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Week starting (Mon)</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Week %</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Week P&amp;L (Rs)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>13-Jul-2026</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="14" t="n">
-        <v>-0.027176</v>
-      </c>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="19" t="n">
-        <v>-0.027176</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>-543.52</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>07-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="14" t="n">
-        <v>-0.0163390294647336</v>
-      </c>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="19" t="n">
-        <v>-0.0163390294647336</v>
-      </c>
-      <c r="H16" s="20" t="n">
-        <v>-317.9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>28-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="14" t="n">
-        <v>-0.02474582753788421</v>
-      </c>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="19" t="n">
-        <v>-0.02474582753788421</v>
-      </c>
-      <c r="H17" s="20" t="n">
-        <v>-473.6</v>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>01-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="13" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="18" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>-206.92</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>08-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="13" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="18" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>-731.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="23" t="n"/>
+          <t>26-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="13" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="18" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>-287.01</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="23" t="n"/>
+          <t>06-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="14" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="20" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>236.98</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>5 (100.0%)</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="23" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B23" s="26" t="n">
-        <v>-1335.02</v>
-      </c>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="23" t="n"/>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="13" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="18" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>-231.31</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="23" t="n"/>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="n">
-        <v>-1335.02</v>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="C25" s="22" t="n"/>
       <c r="D25" s="23" t="n"/>
@@ -2810,11 +2838,13 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="n">
-        <v>271.02</v>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>1 (14.3%)</t>
+        </is>
       </c>
       <c r="C26" s="22" t="n"/>
       <c r="D26" s="23" t="n"/>
@@ -2822,11 +2852,13 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="n">
-        <v>-267</v>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>6 (85.7%)</t>
+        </is>
       </c>
       <c r="C27" s="22" t="n"/>
       <c r="D27" s="23" t="n"/>
@@ -2834,11 +2866,11 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B28" s="28" t="n">
-        <v>-14.84</v>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n">
+        <v>-1219.59</v>
       </c>
       <c r="C28" s="22" t="n"/>
       <c r="D28" s="23" t="n"/>
@@ -2846,11 +2878,11 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
+          <t>Total Profit (Rs)</t>
         </is>
       </c>
       <c r="B29" s="25" t="n">
-        <v>0</v>
+        <v>236.98</v>
       </c>
       <c r="C29" s="22" t="n"/>
       <c r="D29" s="23" t="n"/>
@@ -2858,11 +2890,11 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B30" s="29" t="n">
-        <v>0</v>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n">
+        <v>-1456.57</v>
       </c>
       <c r="C30" s="22" t="n"/>
       <c r="D30" s="23" t="n"/>
@@ -2870,11 +2902,11 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="n">
-        <v>-267</v>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="n">
+        <v>348.39</v>
       </c>
       <c r="C31" s="22" t="n"/>
       <c r="D31" s="23" t="n"/>
@@ -2882,11 +2914,11 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B32" s="30" t="n">
-        <v>-14.84</v>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n">
+        <v>-174.23</v>
       </c>
       <c r="C32" s="22" t="n"/>
       <c r="D32" s="23" t="n"/>
@@ -2894,11 +2926,11 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="n">
-        <v>-216.68</v>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n">
+        <v>-10.42</v>
       </c>
       <c r="C33" s="22" t="n"/>
       <c r="D33" s="23" t="n"/>
@@ -2906,11 +2938,11 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="n">
-        <v>-317.9</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="n">
+        <v>236.98</v>
       </c>
       <c r="C34" s="22" t="n"/>
       <c r="D34" s="23" t="n"/>
@@ -2918,11 +2950,11 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="n">
-        <v>0</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="n">
+        <v>16.17</v>
       </c>
       <c r="C35" s="22" t="n"/>
       <c r="D35" s="23" t="n"/>
@@ -2930,11 +2962,11 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="n">
-        <v>5</v>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n">
+        <v>-242.76</v>
       </c>
       <c r="C36" s="22" t="n"/>
       <c r="D36" s="23" t="n"/>
@@ -2942,11 +2974,11 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B37" s="26" t="n">
-        <v>-317.9</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="n">
+        <v>-14.85</v>
       </c>
       <c r="C37" s="22" t="n"/>
       <c r="D37" s="23" t="n"/>
@@ -2954,11 +2986,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="26" t="n">
-        <v>-1335.02</v>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="n">
+        <v>236.98</v>
       </c>
       <c r="C38" s="22" t="n"/>
       <c r="D38" s="23" t="n"/>
@@ -2966,11 +2998,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B39" s="30" t="n">
-        <v>-6.68</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n">
+        <v>-295.95</v>
       </c>
       <c r="C39" s="22" t="n"/>
       <c r="D39" s="23" t="n"/>
@@ -2978,11 +3010,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B40" s="31" t="n">
-        <v>-1</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="C40" s="22" t="n"/>
       <c r="D40" s="23" t="n"/>
@@ -2990,11 +3022,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B41" s="31" t="n">
-        <v>0</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="C41" s="22" t="n"/>
       <c r="D41" s="23" t="n"/>
@@ -3002,13 +3034,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="n">
+        <v>-295.95</v>
       </c>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="23" t="n"/>
@@ -3016,17 +3046,77 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B43" s="31" t="n">
-        <v>-77.79000000000001</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="n">
+        <v>-1225.26</v>
       </c>
       <c r="C43" s="22" t="n"/>
       <c r="D43" s="23" t="n"/>
     </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B44" s="30" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="23" t="n"/>
+    </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="23" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B46" s="31" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="23" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B47" s="31" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="23" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B48" s="31" t="n">
+        <v>-12.48</v>
+      </c>
+      <c r="C48" s="22" t="n"/>
+      <c r="D48" s="23" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -3035,7 +3125,7 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
@@ -3043,21 +3133,21 @@
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B20:D20"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B47:D47"/>
     <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3070,7 +3160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3183,172 +3273,188 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>0.007486499999999999</v>
-      </c>
+        <v>2025</v>
+      </c>
+      <c r="B5" s="4" t="n"/>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
-      <c r="E5" s="13" t="n">
-        <v>0.007542532827983304</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>0.05840394725370424</v>
-      </c>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
-      <c r="H5" s="14" t="n">
-        <v>-0.07320193545895015</v>
-      </c>
+      <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
-      <c r="J5" s="14" t="n">
-        <v>-0.08522889614546995</v>
-      </c>
+      <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
+      <c r="M5" s="13" t="n">
+        <v>-0.082417</v>
+      </c>
       <c r="N5" s="17" t="n">
-        <v>-0.08914000000000022</v>
-      </c>
-      <c r="O5" s="20" t="n">
-        <v>-1782.8</v>
+        <v>-0.08241699999999996</v>
+      </c>
+      <c r="O5" s="19" t="n">
+        <v>-1648.34</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="n">
-        <v>0.007486499999999999</v>
+      <c r="A6" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>-0.03399801434856575</v>
       </c>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="15" t="n">
-        <v>0.007542532827983304</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>0.05840394725370424</v>
+      <c r="D6" s="13" t="n">
+        <v>-0.004249836696612201</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>0.01342480342616302</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0.03063325839129137</v>
       </c>
       <c r="G6" s="4" t="n"/>
-      <c r="H6" s="17" t="n">
-        <v>-0.07320193545895015</v>
-      </c>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="17" t="n">
-        <v>-0.08522889614546995</v>
-      </c>
-      <c r="K6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="13" t="n">
+        <v>-0.03079177692721151</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>-0.01294427932916501</v>
+      </c>
+      <c r="K6" s="13" t="n">
+        <v>-0.02117146945634402</v>
+      </c>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="N6" s="17" t="n">
+        <v>-0.05921698636526596</v>
+      </c>
+      <c r="O6" s="19" t="n">
+        <v>-1086.73</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>-0.03399801434856575</v>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="17" t="n">
+        <v>-0.004249836696612201</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.01342480342616302</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>0.03063325839129137</v>
+      </c>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="17" t="n">
+        <v>-0.03079177692721151</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>-0.01294427932916501</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>-0.02117146945634402</v>
+      </c>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="17" t="n">
+        <v>-0.082417</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Month %</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Month P&amp;L (Rs)</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jan</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="n">
-        <v>0.007486499999999999</v>
-      </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="18" t="n">
-        <v>0.007486499999999999</v>
-      </c>
-      <c r="I10" s="16" t="n">
-        <v>149.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-Apr</t>
+          <t>2025-Dec</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>0.02240377414486447</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>-0.01453558925808061</v>
-      </c>
-      <c r="D11" s="4" t="n"/>
+        <v>-0.010346</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>-0.03725208860676486</v>
+      </c>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="18" t="n">
-        <v>0.007542532827983304</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>151.98</v>
+        <v>-0.082417</v>
+      </c>
+      <c r="I11" s="19" t="n">
+        <v>-1648.34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-May</t>
+          <t>2026-Jan</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>0.05840394725370424</v>
+        <v>-0.03399801434856575</v>
       </c>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
@@ -3356,390 +3462,424 @@
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="18" t="n">
-        <v>0.05840394725370424</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>1185.7</v>
+        <v>-0.03399801434856575</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>-623.92</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-Jul</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>-0.04929992909477665</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>-0.009823459158335844</v>
-      </c>
+          <t>2026-Mar</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>-0.004249836696612201</v>
+      </c>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
-      <c r="H13" s="19" t="n">
-        <v>-0.07320193545895015</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <v>-1572.92</v>
+      <c r="H13" s="18" t="n">
+        <v>-0.004249836696612201</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>-75.34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-Sep</t>
+          <t>2026-Apr</t>
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>-0.02881419509111205</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>-0.009536898152959539</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>-0.0490190653479653</v>
-      </c>
+        <v>0.01342480342616302</v>
+      </c>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
-      <c r="H14" s="19" t="n">
-        <v>-0.08522889614546995</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>-1697.29</v>
+      <c r="H14" s="20" t="n">
+        <v>0.01342480342616302</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <v>236.98</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-May</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>0.03063325839129137</v>
+      </c>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="20" t="n">
+        <v>0.03063325839129137</v>
+      </c>
+      <c r="I15" s="16" t="n">
+        <v>548.01</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-Aug</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>-0.01924892840038639</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>-0.01176939680320576</v>
+      </c>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="18" t="n">
+        <v>-0.03079177692721151</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>-567.72</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-Sep</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>-0.01294427932916501</v>
+      </c>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="18" t="n">
+        <v>-0.01294427932916501</v>
+      </c>
+      <c r="I17" s="19" t="n">
+        <v>-231.31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>19-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="13" t="n">
-        <v>0.007486499999999999</v>
-      </c>
+          <t>2026-Oct</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>-0.02117146945634402</v>
+      </c>
+      <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
-      <c r="G18" s="18" t="n">
-        <v>0.007486499999999999</v>
-      </c>
-      <c r="H18" s="16" t="n">
-        <v>149.73</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>06-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="13" t="n">
-        <v>0.02240377414486447</v>
-      </c>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="18" t="n">
-        <v>0.02240377414486447</v>
-      </c>
-      <c r="H19" s="16" t="n">
-        <v>451.43</v>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="18" t="n">
+        <v>-0.02117146945634402</v>
+      </c>
+      <c r="I18" s="19" t="n">
+        <v>-373.43</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>20-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="14" t="n">
-        <v>-0.01453558925808061</v>
-      </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="19" t="n">
-        <v>-0.01453558925808061</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>-299.45</v>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="13" t="n">
-        <v>0.05840394725370424</v>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="18" t="n">
-        <v>0.05840394725370424</v>
-      </c>
-      <c r="H21" s="16" t="n">
-        <v>1185.7</v>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>06-Jul-2026</t>
+          <t>01-Dec-2025</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
-      <c r="C22" s="14" t="n">
-        <v>-0.01546998917040258</v>
+      <c r="C22" s="13" t="n">
+        <v>-0.010346</v>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="19" t="n">
-        <v>-0.01546998917040258</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <v>-332.41</v>
+      <c r="G22" s="18" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>-206.92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>13-Jul-2026</t>
+          <t>08-Dec-2025</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
-      <c r="C23" s="14" t="n">
-        <v>-0.04929992909477665</v>
+      <c r="C23" s="13" t="n">
+        <v>-0.0369487719950609</v>
       </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
-      <c r="G23" s="19" t="n">
-        <v>-0.04929992909477665</v>
-      </c>
-      <c r="H23" s="20" t="n">
-        <v>-1042.94</v>
+      <c r="G23" s="18" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>-731.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>27-Jul-2026</t>
+          <t>29-Dec-2025</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
-      <c r="C24" s="14" t="n">
-        <v>-0.009823459158335844</v>
+      <c r="C24" s="13" t="n">
+        <v>-0.03725208860676486</v>
       </c>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
-      <c r="G24" s="19" t="n">
-        <v>-0.009823459158335844</v>
-      </c>
-      <c r="H24" s="20" t="n">
-        <v>-197.57</v>
+      <c r="G24" s="18" t="n">
+        <v>-0.03725208860676486</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>-710.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>26-Jan-2026</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
-      <c r="C25" s="14" t="n">
-        <v>-0.02881419509111205</v>
+      <c r="C25" s="13" t="n">
+        <v>-0.03399801434856575</v>
       </c>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
-      <c r="G25" s="19" t="n">
-        <v>-0.02881419509111205</v>
-      </c>
-      <c r="H25" s="20" t="n">
-        <v>-573.8200000000001</v>
+      <c r="G25" s="18" t="n">
+        <v>-0.03399801434856575</v>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>-623.92</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>14-Sep-2026</t>
+          <t>23-Mar-2026</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
-      <c r="C26" s="14" t="n">
-        <v>-0.009536898152959539</v>
+      <c r="C26" s="13" t="n">
+        <v>-0.004249836696612201</v>
       </c>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
-      <c r="G26" s="19" t="n">
-        <v>-0.009536898152959539</v>
-      </c>
-      <c r="H26" s="20" t="n">
-        <v>-184.45</v>
+      <c r="G26" s="18" t="n">
+        <v>-0.004249836696612201</v>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>-75.34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>06-Apr-2026</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
       <c r="C27" s="14" t="n">
-        <v>-0.0490190653479653</v>
+        <v>0.01342480342616302</v>
       </c>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
-      <c r="G27" s="19" t="n">
-        <v>-0.0490190653479653</v>
-      </c>
-      <c r="H27" s="20" t="n">
-        <v>-939.02</v>
+      <c r="G27" s="20" t="n">
+        <v>0.01342480342616302</v>
+      </c>
+      <c r="H27" s="16" t="n">
+        <v>236.98</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="14" t="n">
+        <v>0.03063325839129137</v>
+      </c>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="20" t="n">
+        <v>0.03063325839129137</v>
+      </c>
+      <c r="H28" s="16" t="n">
+        <v>548.01</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>10-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="13" t="n">
+        <v>-0.01924892840038639</v>
+      </c>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="18" t="n">
+        <v>-0.01924892840038639</v>
+      </c>
+      <c r="H29" s="19" t="n">
+        <v>-354.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="n">
-        <v>22</v>
-      </c>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="23" t="n"/>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="13" t="n">
+        <v>-0.01176939680320576</v>
+      </c>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="18" t="n">
+        <v>-0.01176939680320576</v>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>-212.82</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B31" s="24" t="inlineStr">
-        <is>
-          <t>5 (22.7%)</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="23" t="n"/>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="13" t="n">
+        <v>-0.01294427932916501</v>
+      </c>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="18" t="n">
+        <v>-0.01294427932916501</v>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>-231.31</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B32" s="24" t="inlineStr">
-        <is>
-          <t>17 (77.3%)</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="23" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B33" s="26" t="n">
-        <v>-1782.8</v>
-      </c>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="23" t="n"/>
+          <t>12-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="13" t="n">
+        <v>-0.02117146945634402</v>
+      </c>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="18" t="n">
+        <v>-0.02117146945634402</v>
+      </c>
+      <c r="H32" s="19" t="n">
+        <v>-373.43</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="n">
-        <v>2338.58</v>
-      </c>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="23" t="n"/>
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B35" s="26" t="n">
-        <v>-4121.38</v>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="n">
+        <v>18</v>
       </c>
       <c r="C35" s="22" t="n"/>
       <c r="D35" s="23" t="n"/>
@@ -3747,11 +3887,13 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="n">
-        <v>842.95</v>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>3 (16.7%)</t>
+        </is>
       </c>
       <c r="C36" s="22" t="n"/>
       <c r="D36" s="23" t="n"/>
@@ -3759,11 +3901,13 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B37" s="26" t="n">
-        <v>-81.04000000000001</v>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>15 (83.3%)</t>
+        </is>
       </c>
       <c r="C37" s="22" t="n"/>
       <c r="D37" s="23" t="n"/>
@@ -3771,11 +3915,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B38" s="28" t="n">
-        <v>-3.56</v>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n">
+        <v>-2735.07</v>
       </c>
       <c r="C38" s="22" t="n"/>
       <c r="D38" s="23" t="n"/>
@@ -3783,11 +3927,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
+          <t>Total Profit (Rs)</t>
         </is>
       </c>
       <c r="B39" s="25" t="n">
-        <v>467.72</v>
+        <v>1277.35</v>
       </c>
       <c r="C39" s="22" t="n"/>
       <c r="D39" s="23" t="n"/>
@@ -3795,11 +3939,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B40" s="29" t="n">
-        <v>54.93</v>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n">
+        <v>-4012.42</v>
       </c>
       <c r="C40" s="22" t="n"/>
       <c r="D40" s="23" t="n"/>
@@ -3807,11 +3951,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B41" s="26" t="n">
-        <v>-242.43</v>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="n">
+        <v>856.62</v>
       </c>
       <c r="C41" s="22" t="n"/>
       <c r="D41" s="23" t="n"/>
@@ -3819,11 +3963,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B42" s="30" t="n">
-        <v>-20.76</v>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B42" s="26" t="n">
+        <v>-151.95</v>
       </c>
       <c r="C42" s="22" t="n"/>
       <c r="D42" s="23" t="n"/>
@@ -3831,11 +3975,11 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B43" s="25" t="n">
-        <v>552.97</v>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B43" s="28" t="n">
+        <v>-8.27</v>
       </c>
       <c r="C43" s="22" t="n"/>
       <c r="D43" s="23" t="n"/>
@@ -3843,11 +3987,11 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B44" s="26" t="n">
-        <v>-332.41</v>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="n">
+        <v>425.78</v>
       </c>
       <c r="C44" s="22" t="n"/>
       <c r="D44" s="23" t="n"/>
@@ -3855,11 +3999,11 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B45" s="21" t="n">
-        <v>3</v>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B45" s="29" t="n">
+        <v>42</v>
       </c>
       <c r="C45" s="22" t="n"/>
       <c r="D45" s="23" t="n"/>
@@ -3867,11 +4011,11 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B46" s="21" t="n">
-        <v>14</v>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B46" s="26" t="n">
+        <v>-267.49</v>
       </c>
       <c r="C46" s="22" t="n"/>
       <c r="D46" s="23" t="n"/>
@@ -3879,11 +4023,11 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B47" s="26" t="n">
-        <v>-332.41</v>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B47" s="30" t="n">
+        <v>-18.33</v>
       </c>
       <c r="C47" s="22" t="n"/>
       <c r="D47" s="23" t="n"/>
@@ -3891,11 +4035,11 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B48" s="26" t="n">
-        <v>-3501.72</v>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="n">
+        <v>548.01</v>
       </c>
       <c r="C48" s="22" t="n"/>
       <c r="D48" s="23" t="n"/>
@@ -3903,11 +4047,11 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B49" s="30" t="n">
-        <v>-16.12</v>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B49" s="26" t="n">
+        <v>-358.86</v>
       </c>
       <c r="C49" s="22" t="n"/>
       <c r="D49" s="23" t="n"/>
@@ -3915,11 +4059,11 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B50" s="31" t="n">
-        <v>-0.51</v>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="C50" s="22" t="n"/>
       <c r="D50" s="23" t="n"/>
@@ -3927,11 +4071,11 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B51" s="31" t="n">
-        <v>0.57</v>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="n">
+        <v>12</v>
       </c>
       <c r="C51" s="22" t="n"/>
       <c r="D51" s="23" t="n"/>
@@ -3939,11 +4083,11 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B52" s="31" t="n">
-        <v>1.93</v>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B52" s="26" t="n">
+        <v>-358.86</v>
       </c>
       <c r="C52" s="22" t="n"/>
       <c r="D52" s="23" t="n"/>
@@ -3951,17 +4095,77 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B53" s="31" t="n">
-        <v>-4.54</v>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B53" s="26" t="n">
+        <v>-3213.41</v>
       </c>
       <c r="C53" s="22" t="n"/>
       <c r="D53" s="23" t="n"/>
     </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B54" s="30" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="23" t="n"/>
+    </row>
     <row r="55">
-      <c r="A55" s="11" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B55" s="31" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="23" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B56" s="31" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C56" s="22" t="n"/>
+      <c r="D56" s="23" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B57" s="31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C57" s="22" t="n"/>
+      <c r="D57" s="23" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B58" s="31" t="n">
+        <v>-10.39</v>
+      </c>
+      <c r="C58" s="22" t="n"/>
+      <c r="D58" s="23" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -3970,25 +4174,25 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B57:D57"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B53:D53"/>
     <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B55:D55"/>
     <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B54:D54"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>

--- a/reports/latest_backtest_dashboard.xlsx
+++ b/reports/latest_backtest_dashboard.xlsx
@@ -172,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -186,6 +186,7 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -708,23 +709,31 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>trend_scalp_nw (EMA9/26) [5m]</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>-1219.59</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>-0.06126299999999993</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -739,23 +748,23 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>-2735.07</v>
+        <v>-1515.48</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>-0.1569609630790708</v>
+        <v>-0.09711239423094309</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Each index sheet shows ONLY its single best-performing strategy/EMA combo from this backtest -- not all combos combined (that would double-count the same time period across competing strategies). See latest_backtest_summary.xlsx for every combo.</t>
         </is>
@@ -801,7 +810,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>MONTHLY returns (% of capital at start of month)</t>
         </is>
@@ -890,26 +899,26 @@
       </c>
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="4" t="n"/>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="14" t="n">
         <v>-0.003766999999999999</v>
       </c>
       <c r="E5" s="4" t="n"/>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="15" t="n">
         <v>0.02750410797474085</v>
       </c>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
-      <c r="K5" s="13" t="n">
+      <c r="K5" s="14" t="n">
         <v>-0.009550293146912445</v>
       </c>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
-      <c r="N5" s="15" t="n">
+      <c r="N5" s="16" t="n">
         <v>0.01385750000000008</v>
       </c>
-      <c r="O5" s="16" t="n">
+      <c r="O5" s="17" t="n">
         <v>277.15</v>
       </c>
     </row>
@@ -921,25 +930,25 @@
       </c>
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>-0.003766999999999999</v>
       </c>
       <c r="E6" s="4" t="n"/>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="16" t="n">
         <v>0.02750410797474085</v>
       </c>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
-      <c r="K6" s="17" t="n">
+      <c r="K6" s="18" t="n">
         <v>-0.009550293146912445</v>
       </c>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
         </is>
@@ -998,7 +1007,7 @@
           <t>2026-Mar</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="14" t="n">
         <v>-0.003766999999999999</v>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -1006,10 +1015,10 @@
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
-      <c r="H10" s="18" t="n">
+      <c r="H10" s="19" t="n">
         <v>-0.003766999999999999</v>
       </c>
-      <c r="I10" s="19" t="n">
+      <c r="I10" s="20" t="n">
         <v>-75.34</v>
       </c>
     </row>
@@ -1019,7 +1028,7 @@
           <t>2026-May</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="15" t="n">
         <v>0.02750410797474085</v>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -1027,10 +1036,10 @@
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="21" t="n">
         <v>0.02750410797474085</v>
       </c>
-      <c r="I11" s="16" t="n">
+      <c r="I11" s="17" t="n">
         <v>548.01</v>
       </c>
     </row>
@@ -1040,7 +1049,7 @@
           <t>2026-Oct</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="14" t="n">
         <v>-0.009550293146912445</v>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -1048,15 +1057,15 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="19" t="n">
         <v>-0.009550293146912445</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I12" s="20" t="n">
         <v>-195.52</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
         </is>
@@ -1111,16 +1120,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="14" t="n">
         <v>-0.003766999999999999</v>
       </c>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>-0.003766999999999999</v>
       </c>
-      <c r="H16" s="19" t="n">
+      <c r="H16" s="20" t="n">
         <v>-75.34</v>
       </c>
     </row>
@@ -1131,16 +1140,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="15" t="n">
         <v>0.02750410797474085</v>
       </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
-      <c r="G17" s="20" t="n">
+      <c r="G17" s="21" t="n">
         <v>0.02750410797474085</v>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="17" t="n">
         <v>548.01</v>
       </c>
     </row>
@@ -1151,21 +1160,21 @@
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="14" t="n">
         <v>-0.009550293146912445</v>
       </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="19" t="n">
         <v>-0.009550293146912445</v>
       </c>
-      <c r="H18" s="19" t="n">
+      <c r="H18" s="20" t="n">
         <v>-195.52</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>STATISTICS (all trades for this index)</t>
         </is>
@@ -1177,11 +1186,11 @@
           <t>All trades</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n">
+      <c r="B21" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="23" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="24" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1189,13 +1198,13 @@
           <t>Winners</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>2 (40.0%)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="23" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="24" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1203,13 +1212,13 @@
           <t>Losers</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>3 (60.0%)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="23" t="n"/>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="24" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1217,11 +1226,11 @@
           <t>Net P&amp;L (Rs)</t>
         </is>
       </c>
-      <c r="B24" s="25" t="n">
+      <c r="B24" s="26" t="n">
         <v>277.15</v>
       </c>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="23" t="n"/>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="24" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1229,11 +1238,11 @@
           <t>Total Profit (Rs)</t>
         </is>
       </c>
-      <c r="B25" s="25" t="n">
+      <c r="B25" s="26" t="n">
         <v>1040.37</v>
       </c>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="24" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1241,11 +1250,11 @@
           <t>Total Loss (Rs)</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="27" t="n">
         <v>-763.22</v>
       </c>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="23" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="24" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1253,11 +1262,11 @@
           <t>Transaction costs (Rs)</t>
         </is>
       </c>
-      <c r="B27" s="27" t="n">
+      <c r="B27" s="28" t="n">
         <v>143.6</v>
       </c>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="24" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1265,11 +1274,11 @@
           <t>Avg Profit/Loss per trade (Rs)</t>
         </is>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="26" t="n">
         <v>55.43</v>
       </c>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="23" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="24" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1277,11 +1286,11 @@
           <t>Avg Profit/Loss per trade (% of premium)</t>
         </is>
       </c>
-      <c r="B29" s="28" t="n">
+      <c r="B29" s="29" t="n">
         <v>2.6</v>
       </c>
-      <c r="C29" s="22" t="n"/>
-      <c r="D29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="24" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1289,11 +1298,11 @@
           <t>Avg Win (Rs)</t>
         </is>
       </c>
-      <c r="B30" s="25" t="n">
+      <c r="B30" s="26" t="n">
         <v>520.1799999999999</v>
       </c>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="23" t="n"/>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="24" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1301,11 +1310,11 @@
           <t>Avg Win (% of premium)</t>
         </is>
       </c>
-      <c r="B31" s="29" t="n">
+      <c r="B31" s="30" t="n">
         <v>54.92</v>
       </c>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="23" t="n"/>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="24" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1313,11 +1322,11 @@
           <t>Avg Loss (Rs)</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="27" t="n">
         <v>-254.41</v>
       </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="23" t="n"/>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="24" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1325,11 +1334,11 @@
           <t>Avg Loss (% of premium)</t>
         </is>
       </c>
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="31" t="n">
         <v>-32.27</v>
       </c>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="23" t="n"/>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="24" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1337,11 +1346,11 @@
           <t>Largest Win (Rs)</t>
         </is>
       </c>
-      <c r="B34" s="25" t="n">
+      <c r="B34" s="26" t="n">
         <v>548.01</v>
       </c>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="23" t="n"/>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="24" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1349,11 +1358,11 @@
           <t>Largest Loss (Rs)</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="27" t="n">
         <v>-299.45</v>
       </c>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="23" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="24" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1361,11 +1370,11 @@
           <t>Max Consecutive Wins</t>
         </is>
       </c>
-      <c r="B36" s="21" t="n">
+      <c r="B36" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="23" t="n"/>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="24" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1373,11 +1382,11 @@
           <t>Max Consecutive Losses</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n">
+      <c r="B37" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="23" t="n"/>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="24" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1385,11 +1394,11 @@
           <t>Max trade drawdown (Rs)</t>
         </is>
       </c>
-      <c r="B38" s="26" t="n">
+      <c r="B38" s="27" t="n">
         <v>-299.45</v>
       </c>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="23" t="n"/>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="24" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1397,11 +1406,11 @@
           <t>Max system drawdown (Rs)</t>
         </is>
       </c>
-      <c r="B39" s="26" t="n">
+      <c r="B39" s="27" t="n">
         <v>-299.45</v>
       </c>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="23" t="n"/>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="24" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1409,11 +1418,11 @@
           <t>Max system drawdown (%)</t>
         </is>
       </c>
-      <c r="B40" s="30" t="n">
+      <c r="B40" s="31" t="n">
         <v>-1.48</v>
       </c>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="23" t="n"/>
+      <c r="C40" s="23" t="n"/>
+      <c r="D40" s="24" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1421,11 +1430,11 @@
           <t>Recovery Factor</t>
         </is>
       </c>
-      <c r="B41" s="31" t="n">
+      <c r="B41" s="32" t="n">
         <v>0.93</v>
       </c>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="23" t="n"/>
+      <c r="C41" s="23" t="n"/>
+      <c r="D41" s="24" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -1433,11 +1442,11 @@
           <t>Profit Factor</t>
         </is>
       </c>
-      <c r="B42" s="31" t="n">
+      <c r="B42" s="32" t="n">
         <v>1.36</v>
       </c>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="23" t="n"/>
+      <c r="C42" s="23" t="n"/>
+      <c r="D42" s="24" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -1445,11 +1454,11 @@
           <t>Payoff Ratio (avg win / avg loss)</t>
         </is>
       </c>
-      <c r="B43" s="31" t="n">
+      <c r="B43" s="32" t="n">
         <v>2.04</v>
       </c>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="23" t="n"/>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="24" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1457,14 +1466,14 @@
           <t>Sharpe Ratio (annualized)</t>
         </is>
       </c>
-      <c r="B44" s="31" t="n">
+      <c r="B44" s="32" t="n">
         <v>4.61</v>
       </c>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="23" t="n"/>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="24" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -1536,7 +1545,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>MONTHLY returns (% of capital at start of month)</t>
         </is>
@@ -1634,13 +1643,13 @@
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="13" t="n">
+      <c r="M5" s="14" t="n">
         <v>-0.0355045</v>
       </c>
-      <c r="N5" s="17" t="n">
+      <c r="N5" s="18" t="n">
         <v>-0.03550450000000005</v>
       </c>
-      <c r="O5" s="19" t="n">
+      <c r="O5" s="20" t="n">
         <v>-710.09</v>
       </c>
     </row>
@@ -1648,7 +1657,7 @@
       <c r="A6" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="14" t="n">
         <v>-0.01746560766742821</v>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -1657,19 +1666,19 @@
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
-      <c r="I6" s="13" t="n">
+      <c r="I6" s="14" t="n">
         <v>-0.02995409697673192</v>
       </c>
       <c r="J6" s="4" t="n"/>
-      <c r="K6" s="13" t="n">
+      <c r="K6" s="14" t="n">
         <v>-0.009676763149650155</v>
       </c>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="17" t="n">
+      <c r="N6" s="18" t="n">
         <v>-0.05611949459587939</v>
       </c>
-      <c r="O6" s="19" t="n">
+      <c r="O6" s="20" t="n">
         <v>-1082.54</v>
       </c>
     </row>
@@ -1679,7 +1688,7 @@
           <t>Avg</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>-0.01746560766742821</v>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -1688,20 +1697,20 @@
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
-      <c r="I7" s="17" t="n">
+      <c r="I7" s="18" t="n">
         <v>-0.02995409697673192</v>
       </c>
       <c r="J7" s="4" t="n"/>
-      <c r="K7" s="17" t="n">
+      <c r="K7" s="18" t="n">
         <v>-0.009676763149650155</v>
       </c>
       <c r="L7" s="4" t="n"/>
-      <c r="M7" s="17" t="n">
+      <c r="M7" s="18" t="n">
         <v>-0.0355045</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
         </is>
@@ -1760,7 +1769,7 @@
           <t>2025-Dec</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="14" t="n">
         <v>-0.0355045</v>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -1768,10 +1777,10 @@
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="18" t="n">
+      <c r="H11" s="19" t="n">
         <v>-0.0355045</v>
       </c>
-      <c r="I11" s="19" t="n">
+      <c r="I11" s="20" t="n">
         <v>-710.09</v>
       </c>
     </row>
@@ -1781,7 +1790,7 @@
           <t>2026-Jan</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="14" t="n">
         <v>-0.01746560766742821</v>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -1789,10 +1798,10 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="19" t="n">
         <v>-0.01746560766742821</v>
       </c>
-      <c r="I12" s="19" t="n">
+      <c r="I12" s="20" t="n">
         <v>-336.91</v>
       </c>
     </row>
@@ -1802,20 +1811,20 @@
           <t>2026-Aug</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="14" t="n">
         <v>-0.01872526776763573</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="14" t="n">
         <v>-0.01144310440313796</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="19" t="n">
         <v>-0.02995409697673192</v>
       </c>
-      <c r="I13" s="19" t="n">
+      <c r="I13" s="20" t="n">
         <v>-567.72</v>
       </c>
     </row>
@@ -1825,7 +1834,7 @@
           <t>2026-Oct</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="14" t="n">
         <v>-0.009676763149650155</v>
       </c>
       <c r="C14" s="4" t="n"/>
@@ -1833,15 +1842,15 @@
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
-      <c r="H14" s="18" t="n">
+      <c r="H14" s="19" t="n">
         <v>-0.009676763149650155</v>
       </c>
-      <c r="I14" s="19" t="n">
+      <c r="I14" s="20" t="n">
         <v>-177.91</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
         </is>
@@ -1896,16 +1905,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="14" t="n">
         <v>-0.0355045</v>
       </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
-      <c r="G18" s="18" t="n">
+      <c r="G18" s="19" t="n">
         <v>-0.0355045</v>
       </c>
-      <c r="H18" s="19" t="n">
+      <c r="H18" s="20" t="n">
         <v>-710.09</v>
       </c>
     </row>
@@ -1916,16 +1925,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="14" t="n">
         <v>-0.01746560766742821</v>
       </c>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
-      <c r="G19" s="18" t="n">
+      <c r="G19" s="19" t="n">
         <v>-0.01746560766742821</v>
       </c>
-      <c r="H19" s="19" t="n">
+      <c r="H19" s="20" t="n">
         <v>-336.91</v>
       </c>
     </row>
@@ -1936,16 +1945,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="14" t="n">
         <v>-0.01872526776763573</v>
       </c>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="18" t="n">
+      <c r="G20" s="19" t="n">
         <v>-0.01872526776763573</v>
       </c>
-      <c r="H20" s="19" t="n">
+      <c r="H20" s="20" t="n">
         <v>-354.9</v>
       </c>
     </row>
@@ -1956,16 +1965,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="14" t="n">
         <v>-0.01144310440313796</v>
       </c>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
-      <c r="G21" s="18" t="n">
+      <c r="G21" s="19" t="n">
         <v>-0.01144310440313796</v>
       </c>
-      <c r="H21" s="19" t="n">
+      <c r="H21" s="20" t="n">
         <v>-212.82</v>
       </c>
     </row>
@@ -1976,21 +1985,21 @@
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="14" t="n">
         <v>-0.009676763149650155</v>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="18" t="n">
+      <c r="G22" s="19" t="n">
         <v>-0.009676763149650155</v>
       </c>
-      <c r="H22" s="19" t="n">
+      <c r="H22" s="20" t="n">
         <v>-177.91</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>STATISTICS (all trades for this index)</t>
         </is>
@@ -2002,11 +2011,11 @@
           <t>All trades</t>
         </is>
       </c>
-      <c r="B25" s="21" t="n">
+      <c r="B25" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="24" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -2014,13 +2023,13 @@
           <t>Winners</t>
         </is>
       </c>
-      <c r="B26" s="24" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="23" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="24" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -2028,13 +2037,13 @@
           <t>Losers</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>6 (100.0%)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="24" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2042,11 +2051,11 @@
           <t>Net P&amp;L (Rs)</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="27" t="n">
         <v>-1792.63</v>
       </c>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="23" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="24" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -2054,11 +2063,11 @@
           <t>Total Profit (Rs)</t>
         </is>
       </c>
-      <c r="B29" s="25" t="n">
+      <c r="B29" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="22" t="n"/>
-      <c r="D29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="24" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -2066,11 +2075,11 @@
           <t>Total Loss (Rs)</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="27" t="n">
         <v>-1792.63</v>
       </c>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="23" t="n"/>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="24" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -2078,11 +2087,11 @@
           <t>Transaction costs (Rs)</t>
         </is>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="28" t="n">
         <v>364.63</v>
       </c>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="23" t="n"/>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="24" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -2090,11 +2099,11 @@
           <t>Avg Profit/Loss per trade (Rs)</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="27" t="n">
         <v>-298.77</v>
       </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="23" t="n"/>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="24" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -2102,11 +2111,11 @@
           <t>Avg Profit/Loss per trade (% of premium)</t>
         </is>
       </c>
-      <c r="B33" s="28" t="n">
+      <c r="B33" s="29" t="n">
         <v>-14.84</v>
       </c>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="23" t="n"/>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="24" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -2114,11 +2123,11 @@
           <t>Avg Win (Rs)</t>
         </is>
       </c>
-      <c r="B34" s="25" t="n">
+      <c r="B34" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="23" t="n"/>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="24" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -2126,11 +2135,11 @@
           <t>Avg Win (% of premium)</t>
         </is>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="23" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="24" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -2138,11 +2147,11 @@
           <t>Avg Loss (Rs)</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="27" t="n">
         <v>-298.77</v>
       </c>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="23" t="n"/>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="24" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -2150,11 +2159,11 @@
           <t>Avg Loss (% of premium)</t>
         </is>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="31" t="n">
         <v>-14.84</v>
       </c>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="23" t="n"/>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="24" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -2162,11 +2171,11 @@
           <t>Largest Win (Rs)</t>
         </is>
       </c>
-      <c r="B38" s="25" t="n">
+      <c r="B38" s="26" t="n">
         <v>-177.91</v>
       </c>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="23" t="n"/>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="24" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2174,11 +2183,11 @@
           <t>Largest Loss (Rs)</t>
         </is>
       </c>
-      <c r="B39" s="26" t="n">
+      <c r="B39" s="27" t="n">
         <v>-358.86</v>
       </c>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="23" t="n"/>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="24" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -2186,11 +2195,11 @@
           <t>Max Consecutive Wins</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n">
+      <c r="B40" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="23" t="n"/>
+      <c r="C40" s="23" t="n"/>
+      <c r="D40" s="24" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -2198,11 +2207,11 @@
           <t>Max Consecutive Losses</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n">
+      <c r="B41" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="23" t="n"/>
+      <c r="C41" s="23" t="n"/>
+      <c r="D41" s="24" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -2210,11 +2219,11 @@
           <t>Max trade drawdown (Rs)</t>
         </is>
       </c>
-      <c r="B42" s="26" t="n">
+      <c r="B42" s="27" t="n">
         <v>-358.86</v>
       </c>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="23" t="n"/>
+      <c r="C42" s="23" t="n"/>
+      <c r="D42" s="24" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -2222,11 +2231,11 @@
           <t>Max system drawdown (Rs)</t>
         </is>
       </c>
-      <c r="B43" s="26" t="n">
+      <c r="B43" s="27" t="n">
         <v>-1792.63</v>
       </c>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="23" t="n"/>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="24" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2234,11 +2243,11 @@
           <t>Max system drawdown (%)</t>
         </is>
       </c>
-      <c r="B44" s="30" t="n">
+      <c r="B44" s="31" t="n">
         <v>-8.960000000000001</v>
       </c>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="23" t="n"/>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="24" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2246,11 +2255,11 @@
           <t>Recovery Factor</t>
         </is>
       </c>
-      <c r="B45" s="31" t="n">
+      <c r="B45" s="32" t="n">
         <v>-1</v>
       </c>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="23" t="n"/>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="24" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -2258,11 +2267,11 @@
           <t>Profit Factor</t>
         </is>
       </c>
-      <c r="B46" s="31" t="n">
+      <c r="B46" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="23" t="n"/>
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="24" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -2270,13 +2279,13 @@
           <t>Payoff Ratio (avg win / avg loss)</t>
         </is>
       </c>
-      <c r="B47" s="24" t="inlineStr">
+      <c r="B47" s="25" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="23" t="n"/>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="24" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -2284,14 +2293,14 @@
           <t>Sharpe Ratio (annualized)</t>
         </is>
       </c>
-      <c r="B48" s="31" t="n">
+      <c r="B48" s="32" t="n">
         <v>-32.23</v>
       </c>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="23" t="n"/>
+      <c r="C48" s="23" t="n"/>
+      <c r="D48" s="24" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -2335,7 +2344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2358,797 +2367,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FINNIFTY -- best: trend_scalp_nw (EMA9/26) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>FINNIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>MONTHLY returns (% of capital at start of month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Yr %</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Yr P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="13" t="n">
-        <v>-0.0469125</v>
-      </c>
-      <c r="N5" s="17" t="n">
-        <v>-0.04691250000000002</v>
-      </c>
-      <c r="O5" s="19" t="n">
-        <v>-938.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="14" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="13" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="17" t="n">
-        <v>-0.01475940036985068</v>
-      </c>
-      <c r="O6" s="19" t="n">
-        <v>-281.34</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="15" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="17" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="17" t="n">
-        <v>-0.0469125</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2025-Dec</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="18" t="n">
-        <v>-0.0469125</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>-938.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-Jan</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="18" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="I12" s="19" t="n">
-        <v>-287.01</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>2026-Apr</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="20" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>236.98</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="18" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="I14" s="19" t="n">
-        <v>-231.31</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>01-Dec-2025</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="13" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="18" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="H18" s="19" t="n">
-        <v>-206.92</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>08-Dec-2025</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="13" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="18" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="H19" s="19" t="n">
-        <v>-731.33</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>26-Jan-2026</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="13" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="18" t="n">
-        <v>-0.01505685469592246</v>
-      </c>
-      <c r="H20" s="19" t="n">
-        <v>-287.01</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>06-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="14" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="20" t="n">
-        <v>0.01262227865738753</v>
-      </c>
-      <c r="H21" s="16" t="n">
-        <v>236.98</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>07-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="13" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="18" t="n">
-        <v>-0.01216670559002552</v>
-      </c>
-      <c r="H22" s="19" t="n">
-        <v>-231.31</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="23" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>1 (14.3%)</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="23" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>6 (85.7%)</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="23" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="n">
-        <v>-1219.59</v>
-      </c>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="23" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B29" s="25" t="n">
-        <v>236.98</v>
-      </c>
-      <c r="C29" s="22" t="n"/>
-      <c r="D29" s="23" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="n">
-        <v>-1456.57</v>
-      </c>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="23" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B31" s="27" t="n">
-        <v>348.39</v>
-      </c>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="23" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="n">
-        <v>-174.23</v>
-      </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="23" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B33" s="28" t="n">
-        <v>-10.42</v>
-      </c>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="23" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="n">
-        <v>236.98</v>
-      </c>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="23" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B35" s="29" t="n">
-        <v>16.17</v>
-      </c>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="23" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B36" s="26" t="n">
-        <v>-242.76</v>
-      </c>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="23" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B37" s="30" t="n">
-        <v>-14.85</v>
-      </c>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="23" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="25" t="n">
-        <v>236.98</v>
-      </c>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="23" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B39" s="26" t="n">
-        <v>-295.95</v>
-      </c>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="23" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B40" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="23" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B41" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="23" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B42" s="26" t="n">
-        <v>-295.95</v>
-      </c>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="23" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B43" s="26" t="n">
-        <v>-1225.26</v>
-      </c>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="23" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B44" s="30" t="n">
-        <v>-6.13</v>
-      </c>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="23" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B45" s="31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="23" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B46" s="31" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="23" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B47" s="31" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="23" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B48" s="31" t="n">
-        <v>-12.48</v>
-      </c>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="23" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
+          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B48:D48"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3160,7 +2390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3188,7 +2418,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>MONTHLY returns (% of capital at start of month)</t>
         </is>
@@ -3286,51 +2516,47 @@
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="13" t="n">
-        <v>-0.082417</v>
-      </c>
-      <c r="N5" s="17" t="n">
-        <v>-0.08241699999999996</v>
-      </c>
-      <c r="O5" s="19" t="n">
-        <v>-1648.34</v>
+      <c r="M5" s="14" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="N5" s="18" t="n">
+        <v>-0.03550450000000005</v>
+      </c>
+      <c r="O5" s="20" t="n">
+        <v>-710.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="B6" s="13" t="n">
-        <v>-0.03399801434856575</v>
+      <c r="B6" s="14" t="n">
+        <v>-0.01746560766742821</v>
       </c>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="13" t="n">
-        <v>-0.004249836696612201</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>0.01342480342616302</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>0.03063325839129137</v>
+      <c r="D6" s="14" t="n">
+        <v>-0.00397509629082467</v>
+      </c>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="15" t="n">
+        <v>0.02902955133210366</v>
       </c>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
-      <c r="I6" s="13" t="n">
-        <v>-0.03079177692721151</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>-0.01294427932916501</v>
-      </c>
-      <c r="K6" s="13" t="n">
-        <v>-0.02117146945634402</v>
+      <c r="I6" s="14" t="n">
+        <v>-0.02922524679972429</v>
+      </c>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="14" t="n">
+        <v>-0.01980225846393696</v>
       </c>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="17" t="n">
-        <v>-0.05921698636526596</v>
-      </c>
-      <c r="O6" s="19" t="n">
-        <v>-1086.73</v>
+      <c r="N6" s="18" t="n">
+        <v>-0.04175187960959892</v>
+      </c>
+      <c r="O6" s="20" t="n">
+        <v>-805.39</v>
       </c>
     </row>
     <row r="7">
@@ -3339,37 +2565,33 @@
           <t>Avg</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
-        <v>-0.03399801434856575</v>
+      <c r="B7" s="18" t="n">
+        <v>-0.01746560766742821</v>
       </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="17" t="n">
-        <v>-0.004249836696612201</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.01342480342616302</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>0.03063325839129137</v>
+      <c r="D7" s="18" t="n">
+        <v>-0.00397509629082467</v>
+      </c>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="16" t="n">
+        <v>0.02902955133210366</v>
       </c>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
-      <c r="I7" s="17" t="n">
-        <v>-0.03079177692721151</v>
-      </c>
-      <c r="J7" s="17" t="n">
-        <v>-0.01294427932916501</v>
-      </c>
-      <c r="K7" s="17" t="n">
-        <v>-0.02117146945634402</v>
+      <c r="I7" s="18" t="n">
+        <v>-0.02922524679972429</v>
+      </c>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="18" t="n">
+        <v>-0.01980225846393696</v>
       </c>
       <c r="L7" s="4" t="n"/>
-      <c r="M7" s="17" t="n">
-        <v>-0.082417</v>
+      <c r="M7" s="18" t="n">
+        <v>-0.0355045</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
         </is>
@@ -3428,23 +2650,19 @@
           <t>2025-Dec</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>-0.03725208860676486</v>
-      </c>
+      <c r="B11" s="14" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="18" t="n">
-        <v>-0.082417</v>
-      </c>
-      <c r="I11" s="19" t="n">
-        <v>-1648.34</v>
+      <c r="H11" s="19" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>-710.09</v>
       </c>
     </row>
     <row r="12">
@@ -3453,19 +2671,19 @@
           <t>2026-Jan</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
-        <v>-0.03399801434856575</v>
+      <c r="B12" s="14" t="n">
+        <v>-0.01746560766742821</v>
       </c>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="18" t="n">
-        <v>-0.03399801434856575</v>
-      </c>
-      <c r="I12" s="19" t="n">
-        <v>-623.92</v>
+      <c r="H12" s="19" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>-336.91</v>
       </c>
     </row>
     <row r="13">
@@ -3474,698 +2692,576 @@
           <t>2026-Mar</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
-        <v>-0.004249836696612201</v>
+      <c r="B13" s="14" t="n">
+        <v>-0.00397509629082467</v>
       </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
-      <c r="H13" s="18" t="n">
-        <v>-0.004249836696612201</v>
-      </c>
-      <c r="I13" s="19" t="n">
+      <c r="H13" s="19" t="n">
+        <v>-0.00397509629082467</v>
+      </c>
+      <c r="I13" s="20" t="n">
         <v>-75.34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-Apr</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>0.01342480342616302</v>
+          <t>2026-May</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>0.02902955133210366</v>
       </c>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
-      <c r="H14" s="20" t="n">
-        <v>0.01342480342616302</v>
-      </c>
-      <c r="I14" s="16" t="n">
-        <v>236.98</v>
+      <c r="H14" s="21" t="n">
+        <v>0.02902955133210366</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>548.01</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-May</t>
+          <t>2026-Aug</t>
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>0.03063325839129137</v>
-      </c>
-      <c r="C15" s="4" t="n"/>
+        <v>-0.01826964012052094</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>-0.01115948648114366</v>
+      </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
       <c r="G15" s="4" t="n"/>
-      <c r="H15" s="20" t="n">
-        <v>0.03063325839129137</v>
-      </c>
-      <c r="I15" s="16" t="n">
-        <v>548.01</v>
+      <c r="H15" s="19" t="n">
+        <v>-0.02922524679972429</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>-567.72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-Aug</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n">
-        <v>-0.01924892840038639</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>-0.01176939680320576</v>
-      </c>
+          <t>2026-Oct</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>-0.01980225846393696</v>
+      </c>
+      <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
-      <c r="H16" s="18" t="n">
-        <v>-0.03079177692721151</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <v>-567.72</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026-Sep</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>-0.01294427932916501</v>
-      </c>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="18" t="n">
-        <v>-0.01294427932916501</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <v>-231.31</v>
+      <c r="H16" s="19" t="n">
+        <v>-0.01980225846393696</v>
+      </c>
+      <c r="I16" s="20" t="n">
+        <v>-373.43</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>2026-Oct</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n">
-        <v>-0.02117146945634402</v>
-      </c>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="18" t="n">
-        <v>-0.02117146945634402</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <v>-373.43</v>
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>29-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="14" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="19" t="n">
+        <v>-0.0355045</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>-710.09</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>26-Jan-2026</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="14" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="19" t="n">
+        <v>-0.01746560766742821</v>
+      </c>
+      <c r="H21" s="20" t="n">
+        <v>-336.91</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>01-Dec-2025</t>
+          <t>23-Mar-2026</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
-      <c r="C22" s="13" t="n">
-        <v>-0.010346</v>
+      <c r="C22" s="14" t="n">
+        <v>-0.00397509629082467</v>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="18" t="n">
-        <v>-0.010346</v>
-      </c>
-      <c r="H22" s="19" t="n">
-        <v>-206.92</v>
+      <c r="G22" s="19" t="n">
+        <v>-0.00397509629082467</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>-75.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>08-Dec-2025</t>
+          <t>11-May-2026</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
-      <c r="C23" s="13" t="n">
-        <v>-0.0369487719950609</v>
+      <c r="C23" s="15" t="n">
+        <v>0.02902955133210366</v>
       </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
-      <c r="G23" s="18" t="n">
-        <v>-0.0369487719950609</v>
-      </c>
-      <c r="H23" s="19" t="n">
-        <v>-731.33</v>
+      <c r="G23" s="21" t="n">
+        <v>0.02902955133210366</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>548.01</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>29-Dec-2025</t>
+          <t>10-Aug-2026</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
-      <c r="C24" s="13" t="n">
-        <v>-0.03725208860676486</v>
+      <c r="C24" s="14" t="n">
+        <v>-0.01826964012052094</v>
       </c>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
-      <c r="G24" s="18" t="n">
-        <v>-0.03725208860676486</v>
-      </c>
-      <c r="H24" s="19" t="n">
-        <v>-710.09</v>
+      <c r="G24" s="19" t="n">
+        <v>-0.01826964012052094</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <v>-354.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26-Jan-2026</t>
+          <t>24-Aug-2026</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
-      <c r="C25" s="13" t="n">
-        <v>-0.03399801434856575</v>
+      <c r="C25" s="14" t="n">
+        <v>-0.01115948648114366</v>
       </c>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
-      <c r="G25" s="18" t="n">
-        <v>-0.03399801434856575</v>
-      </c>
-      <c r="H25" s="19" t="n">
-        <v>-623.92</v>
+      <c r="G25" s="19" t="n">
+        <v>-0.01115948648114366</v>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>-212.82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>23-Mar-2026</t>
+          <t>12-Oct-2026</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
-      <c r="C26" s="13" t="n">
-        <v>-0.004249836696612201</v>
+      <c r="C26" s="14" t="n">
+        <v>-0.01980225846393696</v>
       </c>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
-      <c r="G26" s="18" t="n">
-        <v>-0.004249836696612201</v>
-      </c>
-      <c r="H26" s="19" t="n">
-        <v>-75.34</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>06-Apr-2026</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="14" t="n">
-        <v>0.01342480342616302</v>
-      </c>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="20" t="n">
-        <v>0.01342480342616302</v>
-      </c>
-      <c r="H27" s="16" t="n">
-        <v>236.98</v>
+      <c r="G26" s="19" t="n">
+        <v>-0.01980225846393696</v>
+      </c>
+      <c r="H26" s="20" t="n">
+        <v>-373.43</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="14" t="n">
-        <v>0.03063325839129137</v>
-      </c>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="20" t="n">
-        <v>0.03063325839129137</v>
-      </c>
-      <c r="H28" s="16" t="n">
-        <v>548.01</v>
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>10-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="13" t="n">
-        <v>-0.01924892840038639</v>
-      </c>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="18" t="n">
-        <v>-0.01924892840038639</v>
-      </c>
-      <c r="H29" s="19" t="n">
-        <v>-354.9</v>
-      </c>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="24" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>24-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="13" t="n">
-        <v>-0.01176939680320576</v>
-      </c>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="18" t="n">
-        <v>-0.01176939680320576</v>
-      </c>
-      <c r="H30" s="19" t="n">
-        <v>-212.82</v>
-      </c>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>2 (18.2%)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="24" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="13" t="n">
-        <v>-0.01294427932916501</v>
-      </c>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="18" t="n">
-        <v>-0.01294427932916501</v>
-      </c>
-      <c r="H31" s="19" t="n">
-        <v>-231.31</v>
-      </c>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>9 (81.8%)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="24" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>12-Oct-2026</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="13" t="n">
-        <v>-0.02117146945634402</v>
-      </c>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="18" t="n">
-        <v>-0.02117146945634402</v>
-      </c>
-      <c r="H32" s="19" t="n">
-        <v>-373.43</v>
-      </c>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="n">
+        <v>-1515.48</v>
+      </c>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="24" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n">
+        <v>1040.37</v>
+      </c>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="24" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="n">
+        <v>-2555.85</v>
+      </c>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="24" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="n">
-        <v>18</v>
-      </c>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="23" t="n"/>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B35" s="28" t="n">
+        <v>508.23</v>
+      </c>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="24" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>3 (16.7%)</t>
-        </is>
-      </c>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="23" t="n"/>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="n">
+        <v>-137.77</v>
+      </c>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="24" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>15 (83.3%)</t>
-        </is>
-      </c>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="23" t="n"/>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B37" s="29" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="24" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
+          <t>Avg Win (Rs)</t>
         </is>
       </c>
       <c r="B38" s="26" t="n">
-        <v>-2735.07</v>
-      </c>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="23" t="n"/>
+        <v>520.1799999999999</v>
+      </c>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="24" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B39" s="25" t="n">
-        <v>1277.35</v>
-      </c>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="23" t="n"/>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="24" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B40" s="26" t="n">
-        <v>-4012.42</v>
-      </c>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="23" t="n"/>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="n">
+        <v>-283.98</v>
+      </c>
+      <c r="C40" s="23" t="n"/>
+      <c r="D40" s="24" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B41" s="27" t="n">
-        <v>856.62</v>
-      </c>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="23" t="n"/>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="n">
+        <v>-20.65</v>
+      </c>
+      <c r="C41" s="23" t="n"/>
+      <c r="D41" s="24" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
+          <t>Largest Win (Rs)</t>
         </is>
       </c>
       <c r="B42" s="26" t="n">
-        <v>-151.95</v>
-      </c>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="23" t="n"/>
+        <v>548.01</v>
+      </c>
+      <c r="C42" s="23" t="n"/>
+      <c r="D42" s="24" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B43" s="28" t="n">
-        <v>-8.27</v>
-      </c>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="23" t="n"/>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="n">
+        <v>-358.86</v>
+      </c>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="24" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B44" s="25" t="n">
-        <v>425.78</v>
-      </c>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="23" t="n"/>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="24" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B45" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="23" t="n"/>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="24" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B46" s="26" t="n">
-        <v>-267.49</v>
-      </c>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="23" t="n"/>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="n">
+        <v>-358.86</v>
+      </c>
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="24" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B47" s="30" t="n">
-        <v>-18.33</v>
-      </c>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="23" t="n"/>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="n">
+        <v>-1988.15</v>
+      </c>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="24" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="n">
-        <v>548.01</v>
-      </c>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="23" t="n"/>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B48" s="31" t="n">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="C48" s="23" t="n"/>
+      <c r="D48" s="24" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B49" s="26" t="n">
-        <v>-358.86</v>
-      </c>
-      <c r="C49" s="22" t="n"/>
-      <c r="D49" s="23" t="n"/>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B49" s="32" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="C49" s="23" t="n"/>
+      <c r="D49" s="24" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B50" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="23" t="n"/>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="C50" s="23" t="n"/>
+      <c r="D50" s="24" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B51" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="C51" s="22" t="n"/>
-      <c r="D51" s="23" t="n"/>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B51" s="32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C51" s="23" t="n"/>
+      <c r="D51" s="24" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B52" s="26" t="n">
-        <v>-358.86</v>
-      </c>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="23" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B53" s="26" t="n">
-        <v>-3213.41</v>
-      </c>
-      <c r="C53" s="22" t="n"/>
-      <c r="D53" s="23" t="n"/>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B52" s="32" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="C52" s="23" t="n"/>
+      <c r="D52" s="24" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B54" s="30" t="n">
-        <v>-15.7</v>
-      </c>
-      <c r="C54" s="22" t="n"/>
-      <c r="D54" s="23" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B55" s="31" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="C55" s="22" t="n"/>
-      <c r="D55" s="23" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B56" s="31" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="C56" s="22" t="n"/>
-      <c r="D56" s="23" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B57" s="31" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="C57" s="22" t="n"/>
-      <c r="D57" s="23" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B58" s="31" t="n">
-        <v>-10.39</v>
-      </c>
-      <c r="C58" s="22" t="n"/>
-      <c r="D58" s="23" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -4174,25 +3270,25 @@
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B57:D57"/>
     <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="B47:D47"/>
-    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B58:D58"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>

--- a/reports/latest_backtest_dashboard.xlsx
+++ b/reports/latest_backtest_dashboard.xlsx
@@ -53,10 +53,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000B8A00"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="00C00000"/>
     </font>
     <font>
@@ -64,6 +60,10 @@
       <i val="1"/>
       <color rgb="00666666"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000B8A00"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -172,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -180,23 +180,22 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -208,7 +207,7 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,10 +216,10 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -655,23 +654,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>vwap_ema_momentum (EMA9/13) [5m]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>277.15</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>-0.01480658481386824</v>
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -682,23 +689,31 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>trend_scalp_nw (EMA5/21) [5m]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="10" t="n">
-        <v>-1792.63</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>-0.08963150000000004</v>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -709,31 +724,23 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>trend_scalp_nw (EMA9/26) [5m]</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>-1219.59</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>-0.06126299999999993</v>
       </c>
     </row>
     <row r="7">
@@ -747,24 +754,24 @@
           <t>(combined)</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>-1515.48</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>-0.09711239423094309</v>
+      <c r="C7" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>-1219.59</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>-0.06126299999999993</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Each index sheet shows ONLY its single best-performing strategy/EMA combo from this backtest -- not all combos combined (that would double-count the same time period across competing strategies). See latest_backtest_summary.xlsx for every combo.</t>
         </is>
@@ -782,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -805,713 +812,70 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NIFTY -- best: vwap_ema_momentum (EMA9/13) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>NIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>MONTHLY returns (% of capital at start of month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Jul</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Sep</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Oct</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Nov</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Yr %</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Yr P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="14" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="15" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="14" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="16" t="n">
-        <v>0.01385750000000008</v>
-      </c>
-      <c r="O5" s="17" t="n">
-        <v>277.15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Avg</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="18" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="16" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="18" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Month %</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Month P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2026-Mar</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="19" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>-75.34</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2026-May</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="21" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>548.01</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-Oct</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="19" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>-195.52</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>23-Mar-2026</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="14" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="19" t="n">
-        <v>-0.003766999999999999</v>
-      </c>
-      <c r="H16" s="20" t="n">
-        <v>-75.34</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="15" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="21" t="n">
-        <v>0.02750410797474085</v>
-      </c>
-      <c r="H17" s="17" t="n">
-        <v>548.01</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>12-Oct-2026</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="14" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="19" t="n">
-        <v>-0.009550293146912445</v>
-      </c>
-      <c r="H18" s="20" t="n">
-        <v>-195.52</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="24" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>2 (40.0%)</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="24" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="inlineStr">
-        <is>
-          <t>3 (60.0%)</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="n"/>
-      <c r="D23" s="24" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B24" s="26" t="n">
-        <v>277.15</v>
-      </c>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="24" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="n">
-        <v>1040.37</v>
-      </c>
-      <c r="C25" s="23" t="n"/>
-      <c r="D25" s="24" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="n">
-        <v>-763.22</v>
-      </c>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="24" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B27" s="28" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="C27" s="23" t="n"/>
-      <c r="D27" s="24" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="n">
-        <v>55.43</v>
-      </c>
-      <c r="C28" s="23" t="n"/>
-      <c r="D28" s="24" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B29" s="29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="24" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="n">
-        <v>520.1799999999999</v>
-      </c>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="24" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B31" s="30" t="n">
-        <v>54.92</v>
-      </c>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="24" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B32" s="27" t="n">
-        <v>-254.41</v>
-      </c>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="24" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B33" s="31" t="n">
-        <v>-32.27</v>
-      </c>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="24" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="n">
-        <v>548.01</v>
-      </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="24" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B35" s="27" t="n">
-        <v>-299.45</v>
-      </c>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="24" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B36" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="24" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B37" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="24" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B38" s="27" t="n">
-        <v>-299.45</v>
-      </c>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="24" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B39" s="27" t="n">
-        <v>-299.45</v>
-      </c>
-      <c r="C39" s="23" t="n"/>
-      <c r="D39" s="24" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Max system drawdown (%)</t>
-        </is>
-      </c>
-      <c r="B40" s="31" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="C40" s="23" t="n"/>
-      <c r="D40" s="24" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B41" s="32" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="C41" s="23" t="n"/>
-      <c r="D41" s="24" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B42" s="32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C42" s="23" t="n"/>
-      <c r="D42" s="24" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B43" s="32" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="C43" s="23" t="n"/>
-      <c r="D43" s="24" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B44" s="32" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="24" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BANKNIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1540,12 +904,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BANKNIFTY -- best: trend_scalp_nw (EMA5/21) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>FINNIFTY -- best: trend_scalp_nw (EMA9/26) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>MONTHLY returns (% of capital at start of month)</t>
         </is>
@@ -1643,43 +1007,43 @@
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="14" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="N5" s="18" t="n">
-        <v>-0.03550450000000005</v>
-      </c>
-      <c r="O5" s="20" t="n">
-        <v>-710.09</v>
+      <c r="M5" s="13" t="n">
+        <v>-0.0469125</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>-0.04691250000000002</v>
+      </c>
+      <c r="O5" s="15" t="n">
+        <v>-938.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="B6" s="14" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="B6" s="13" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
+      <c r="E6" s="16" t="n">
+        <v>0.01262227865738753</v>
+      </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
-      <c r="I6" s="14" t="n">
-        <v>-0.02995409697673192</v>
-      </c>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="14" t="n">
-        <v>-0.009676763149650155</v>
-      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="13" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="18" t="n">
-        <v>-0.05611949459587939</v>
-      </c>
-      <c r="O6" s="20" t="n">
-        <v>-1082.54</v>
+      <c r="N6" s="14" t="n">
+        <v>-0.01475940036985068</v>
+      </c>
+      <c r="O6" s="15" t="n">
+        <v>-281.34</v>
       </c>
     </row>
     <row r="7">
@@ -1688,29 +1052,29 @@
           <t>Avg</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="B7" s="14" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
+      <c r="E7" s="17" t="n">
+        <v>0.01262227865738753</v>
+      </c>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
-      <c r="I7" s="18" t="n">
-        <v>-0.02995409697673192</v>
-      </c>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="18" t="n">
-        <v>-0.009676763149650155</v>
-      </c>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="14" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
-      <c r="M7" s="18" t="n">
-        <v>-0.0355045</v>
+      <c r="M7" s="14" t="n">
+        <v>-0.0469125</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
         </is>
@@ -1769,19 +1133,21 @@
           <t>2025-Dec</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="C11" s="4" t="n"/>
+      <c r="B11" s="13" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="19" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>-710.09</v>
+      <c r="H11" s="18" t="n">
+        <v>-0.0469125</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>-938.25</v>
       </c>
     </row>
     <row r="12">
@@ -1790,67 +1156,65 @@
           <t>2026-Jan</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="B12" s="13" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="19" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>-336.91</v>
+      <c r="H12" s="18" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>-287.01</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-Aug</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>-0.01872526776763573</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>-0.01144310440313796</v>
-      </c>
+          <t>2026-Apr</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="19" t="n">
-        <v>-0.02995409697673192</v>
+        <v>0.01262227865738753</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>-567.72</v>
+        <v>236.98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-Oct</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>-0.009676763149650155</v>
+          <t>2026-Sep</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>-0.01216670559002552</v>
       </c>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
-      <c r="H14" s="19" t="n">
-        <v>-0.009676763149650155</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>-177.91</v>
+      <c r="H14" s="18" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>-231.31</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
         </is>
@@ -1901,105 +1265,105 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>29-Dec-2025</t>
+          <t>01-Dec-2025</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
-      <c r="C18" s="14" t="n">
-        <v>-0.0355045</v>
+      <c r="C18" s="13" t="n">
+        <v>-0.010346</v>
       </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
-      <c r="G18" s="19" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="H18" s="20" t="n">
-        <v>-710.09</v>
+      <c r="G18" s="18" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>-206.92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26-Jan-2026</t>
+          <t>08-Dec-2025</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
-      <c r="C19" s="14" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="C19" s="13" t="n">
+        <v>-0.0369487719950609</v>
       </c>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
-      <c r="G19" s="19" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="H19" s="20" t="n">
-        <v>-336.91</v>
+      <c r="G19" s="18" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>-731.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>10-Aug-2026</t>
+          <t>26-Jan-2026</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
-      <c r="C20" s="14" t="n">
-        <v>-0.01872526776763573</v>
+      <c r="C20" s="13" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="19" t="n">
-        <v>-0.01872526776763573</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>-354.9</v>
+      <c r="G20" s="18" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-287.01</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>24-Aug-2026</t>
+          <t>06-Apr-2026</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
-      <c r="C21" s="14" t="n">
-        <v>-0.01144310440313796</v>
+      <c r="C21" s="16" t="n">
+        <v>0.01262227865738753</v>
       </c>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="19" t="n">
-        <v>-0.01144310440313796</v>
+        <v>0.01262227865738753</v>
       </c>
       <c r="H21" s="20" t="n">
-        <v>-212.82</v>
+        <v>236.98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>12-Oct-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
-      <c r="C22" s="14" t="n">
-        <v>-0.009676763149650155</v>
+      <c r="C22" s="13" t="n">
+        <v>-0.01216670559002552</v>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="19" t="n">
-        <v>-0.009676763149650155</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <v>-177.91</v>
+      <c r="G22" s="18" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-231.31</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>STATISTICS (all trades for this index)</t>
         </is>
@@ -2011,11 +1375,11 @@
           <t>All trades</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="C25" s="23" t="n"/>
-      <c r="D25" s="24" t="n"/>
+      <c r="B25" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="23" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -2023,13 +1387,13 @@
           <t>Winners</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="24" t="n"/>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>1 (14.3%)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="23" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -2037,13 +1401,13 @@
           <t>Losers</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
-        <is>
-          <t>6 (100.0%)</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="n"/>
-      <c r="D27" s="24" t="n"/>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>6 (85.7%)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="23" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2051,11 +1415,11 @@
           <t>Net P&amp;L (Rs)</t>
         </is>
       </c>
-      <c r="B28" s="27" t="n">
-        <v>-1792.63</v>
-      </c>
-      <c r="C28" s="23" t="n"/>
-      <c r="D28" s="24" t="n"/>
+      <c r="B28" s="25" t="n">
+        <v>-1219.59</v>
+      </c>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="23" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -2064,10 +1428,10 @@
         </is>
       </c>
       <c r="B29" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="24" t="n"/>
+        <v>236.98</v>
+      </c>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="23" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -2075,11 +1439,11 @@
           <t>Total Loss (Rs)</t>
         </is>
       </c>
-      <c r="B30" s="27" t="n">
-        <v>-1792.63</v>
-      </c>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="24" t="n"/>
+      <c r="B30" s="25" t="n">
+        <v>-1456.57</v>
+      </c>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="23" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -2087,11 +1451,11 @@
           <t>Transaction costs (Rs)</t>
         </is>
       </c>
-      <c r="B31" s="28" t="n">
-        <v>364.63</v>
-      </c>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="24" t="n"/>
+      <c r="B31" s="27" t="n">
+        <v>348.39</v>
+      </c>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="23" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -2099,11 +1463,11 @@
           <t>Avg Profit/Loss per trade (Rs)</t>
         </is>
       </c>
-      <c r="B32" s="27" t="n">
-        <v>-298.77</v>
-      </c>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="24" t="n"/>
+      <c r="B32" s="25" t="n">
+        <v>-174.23</v>
+      </c>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="23" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -2111,11 +1475,11 @@
           <t>Avg Profit/Loss per trade (% of premium)</t>
         </is>
       </c>
-      <c r="B33" s="29" t="n">
-        <v>-14.84</v>
-      </c>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="24" t="n"/>
+      <c r="B33" s="28" t="n">
+        <v>-10.42</v>
+      </c>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="23" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -2124,10 +1488,10 @@
         </is>
       </c>
       <c r="B34" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="24" t="n"/>
+        <v>236.98</v>
+      </c>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="23" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -2135,11 +1499,11 @@
           <t>Avg Win (% of premium)</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="24" t="n"/>
+      <c r="B35" s="29" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="23" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -2147,11 +1511,11 @@
           <t>Avg Loss (Rs)</t>
         </is>
       </c>
-      <c r="B36" s="27" t="n">
-        <v>-298.77</v>
-      </c>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="24" t="n"/>
+      <c r="B36" s="25" t="n">
+        <v>-242.76</v>
+      </c>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="23" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -2159,11 +1523,11 @@
           <t>Avg Loss (% of premium)</t>
         </is>
       </c>
-      <c r="B37" s="31" t="n">
-        <v>-14.84</v>
-      </c>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="24" t="n"/>
+      <c r="B37" s="30" t="n">
+        <v>-14.85</v>
+      </c>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="23" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -2172,10 +1536,10 @@
         </is>
       </c>
       <c r="B38" s="26" t="n">
-        <v>-177.91</v>
-      </c>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="24" t="n"/>
+        <v>236.98</v>
+      </c>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="23" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2183,11 +1547,11 @@
           <t>Largest Loss (Rs)</t>
         </is>
       </c>
-      <c r="B39" s="27" t="n">
-        <v>-358.86</v>
-      </c>
-      <c r="C39" s="23" t="n"/>
-      <c r="D39" s="24" t="n"/>
+      <c r="B39" s="25" t="n">
+        <v>-295.95</v>
+      </c>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="23" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -2195,11 +1559,11 @@
           <t>Max Consecutive Wins</t>
         </is>
       </c>
-      <c r="B40" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="23" t="n"/>
-      <c r="D40" s="24" t="n"/>
+      <c r="B40" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="23" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -2207,11 +1571,11 @@
           <t>Max Consecutive Losses</t>
         </is>
       </c>
-      <c r="B41" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="C41" s="23" t="n"/>
-      <c r="D41" s="24" t="n"/>
+      <c r="B41" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="23" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -2219,11 +1583,11 @@
           <t>Max trade drawdown (Rs)</t>
         </is>
       </c>
-      <c r="B42" s="27" t="n">
-        <v>-358.86</v>
-      </c>
-      <c r="C42" s="23" t="n"/>
-      <c r="D42" s="24" t="n"/>
+      <c r="B42" s="25" t="n">
+        <v>-295.95</v>
+      </c>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="23" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -2231,11 +1595,11 @@
           <t>Max system drawdown (Rs)</t>
         </is>
       </c>
-      <c r="B43" s="27" t="n">
-        <v>-1792.63</v>
-      </c>
-      <c r="C43" s="23" t="n"/>
-      <c r="D43" s="24" t="n"/>
+      <c r="B43" s="25" t="n">
+        <v>-1225.26</v>
+      </c>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="23" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2243,11 +1607,11 @@
           <t>Max system drawdown (%)</t>
         </is>
       </c>
-      <c r="B44" s="31" t="n">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="24" t="n"/>
+      <c r="B44" s="30" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="23" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2255,11 +1619,11 @@
           <t>Recovery Factor</t>
         </is>
       </c>
-      <c r="B45" s="32" t="n">
+      <c r="B45" s="31" t="n">
         <v>-1</v>
       </c>
-      <c r="C45" s="23" t="n"/>
-      <c r="D45" s="24" t="n"/>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="23" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -2267,11 +1631,11 @@
           <t>Profit Factor</t>
         </is>
       </c>
-      <c r="B46" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="24" t="n"/>
+      <c r="B46" s="31" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="23" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -2279,13 +1643,11 @@
           <t>Payoff Ratio (avg win / avg loss)</t>
         </is>
       </c>
-      <c r="B47" s="25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C47" s="23" t="n"/>
-      <c r="D47" s="24" t="n"/>
+      <c r="B47" s="31" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="23" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -2293,14 +1655,14 @@
           <t>Sharpe Ratio (annualized)</t>
         </is>
       </c>
-      <c r="B48" s="32" t="n">
-        <v>-32.23</v>
-      </c>
-      <c r="C48" s="23" t="n"/>
-      <c r="D48" s="24" t="n"/>
+      <c r="B48" s="31" t="n">
+        <v>-12.48</v>
+      </c>
+      <c r="C48" s="22" t="n"/>
+      <c r="D48" s="23" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -2338,13 +1700,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2367,58 +1729,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FINNIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>ALL INDICES -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:O54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ALL INDICES -- PAPER TRADE, NOT REAL MONEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>MONTHLY returns (% of capital at start of month)</t>
         </is>
@@ -2516,47 +1832,43 @@
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
-      <c r="M5" s="14" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="N5" s="18" t="n">
-        <v>-0.03550450000000005</v>
-      </c>
-      <c r="O5" s="20" t="n">
-        <v>-710.09</v>
+      <c r="M5" s="13" t="n">
+        <v>-0.0469125</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>-0.04691250000000002</v>
+      </c>
+      <c r="O5" s="15" t="n">
+        <v>-938.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="B6" s="14" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="B6" s="13" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="14" t="n">
-        <v>-0.00397509629082467</v>
-      </c>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="15" t="n">
-        <v>0.02902955133210366</v>
-      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="16" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
-      <c r="I6" s="14" t="n">
-        <v>-0.02922524679972429</v>
-      </c>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="14" t="n">
-        <v>-0.01980225846393696</v>
-      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="13" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="18" t="n">
-        <v>-0.04175187960959892</v>
-      </c>
-      <c r="O6" s="20" t="n">
-        <v>-805.39</v>
+      <c r="N6" s="14" t="n">
+        <v>-0.01475940036985068</v>
+      </c>
+      <c r="O6" s="15" t="n">
+        <v>-281.34</v>
       </c>
     </row>
     <row r="7">
@@ -2565,33 +1877,29 @@
           <t>Avg</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="B7" s="14" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="C7" s="4" t="n"/>
-      <c r="D7" s="18" t="n">
-        <v>-0.00397509629082467</v>
-      </c>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="16" t="n">
-        <v>0.02902955133210366</v>
-      </c>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="17" t="n">
+        <v>0.01262227865738753</v>
+      </c>
+      <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
-      <c r="I7" s="18" t="n">
-        <v>-0.02922524679972429</v>
-      </c>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="18" t="n">
-        <v>-0.01980225846393696</v>
-      </c>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="14" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
-      <c r="M7" s="18" t="n">
-        <v>-0.0355045</v>
+      <c r="M7" s="14" t="n">
+        <v>-0.0469125</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
         </is>
@@ -2650,19 +1958,21 @@
           <t>2025-Dec</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="C11" s="4" t="n"/>
+      <c r="B11" s="13" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="19" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>-710.09</v>
+      <c r="H11" s="18" t="n">
+        <v>-0.0469125</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>-938.25</v>
       </c>
     </row>
     <row r="12">
@@ -2671,29 +1981,29 @@
           <t>2026-Jan</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="B12" s="13" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="19" t="n">
-        <v>-0.01746560766742821</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>-336.91</v>
+      <c r="H12" s="18" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>-287.01</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-Mar</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>-0.00397509629082467</v>
+          <t>2026-Apr</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>0.01262227865738753</v>
       </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
@@ -2701,567 +2011,483 @@
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="19" t="n">
-        <v>-0.00397509629082467</v>
+        <v>0.01262227865738753</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>-75.34</v>
+        <v>236.98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-May</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="n">
-        <v>0.02902955133210366</v>
+          <t>2026-Sep</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>-0.01216670559002552</v>
       </c>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
-      <c r="H14" s="21" t="n">
-        <v>0.02902955133210366</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>548.01</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2026-Aug</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="n">
-        <v>-0.01826964012052094</v>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>-0.01115948648114366</v>
-      </c>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="19" t="n">
-        <v>-0.02922524679972429</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>-567.72</v>
+      <c r="H14" s="18" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>-231.31</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2026-Oct</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>-0.01980225846393696</v>
-      </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="19" t="n">
-        <v>-0.01980225846393696</v>
-      </c>
-      <c r="I16" s="20" t="n">
-        <v>-373.43</v>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
-        </is>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>01-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="13" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="18" t="n">
+        <v>-0.010346</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>-206.92</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Week starting (Mon)</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Week %</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Week P&amp;L (Rs)</t>
-        </is>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>08-Dec-2025</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="13" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="18" t="n">
+        <v>-0.0369487719950609</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>-731.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>29-Dec-2025</t>
+          <t>26-Jan-2026</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
-      <c r="C20" s="14" t="n">
-        <v>-0.0355045</v>
+      <c r="C20" s="13" t="n">
+        <v>-0.01505685469592246</v>
       </c>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="19" t="n">
-        <v>-0.0355045</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>-710.09</v>
+      <c r="G20" s="18" t="n">
+        <v>-0.01505685469592246</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-287.01</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26-Jan-2026</t>
+          <t>06-Apr-2026</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
-      <c r="C21" s="14" t="n">
-        <v>-0.01746560766742821</v>
+      <c r="C21" s="16" t="n">
+        <v>0.01262227865738753</v>
       </c>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="19" t="n">
-        <v>-0.01746560766742821</v>
+        <v>0.01262227865738753</v>
       </c>
       <c r="H21" s="20" t="n">
-        <v>-336.91</v>
+        <v>236.98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>23-Mar-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
-      <c r="C22" s="14" t="n">
-        <v>-0.00397509629082467</v>
+      <c r="C22" s="13" t="n">
+        <v>-0.01216670559002552</v>
       </c>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="19" t="n">
-        <v>-0.00397509629082467</v>
-      </c>
-      <c r="H22" s="20" t="n">
-        <v>-75.34</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>11-May-2026</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="15" t="n">
-        <v>0.02902955133210366</v>
-      </c>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="21" t="n">
-        <v>0.02902955133210366</v>
-      </c>
-      <c r="H23" s="17" t="n">
-        <v>548.01</v>
+      <c r="G22" s="18" t="n">
+        <v>-0.01216670559002552</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-231.31</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>10-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="14" t="n">
-        <v>-0.01826964012052094</v>
-      </c>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="19" t="n">
-        <v>-0.01826964012052094</v>
-      </c>
-      <c r="H24" s="20" t="n">
-        <v>-354.9</v>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>24-Aug-2026</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="14" t="n">
-        <v>-0.01115948648114366</v>
-      </c>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="19" t="n">
-        <v>-0.01115948648114366</v>
-      </c>
-      <c r="H25" s="20" t="n">
-        <v>-212.82</v>
-      </c>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="23" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>12-Oct-2026</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="14" t="n">
-        <v>-0.01980225846393696</v>
-      </c>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="19" t="n">
-        <v>-0.01980225846393696</v>
-      </c>
-      <c r="H26" s="20" t="n">
-        <v>-373.43</v>
-      </c>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>1 (14.3%)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="23" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>6 (85.7%)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="23" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>STATISTICS (all trades for this index)</t>
-        </is>
-      </c>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="n">
+        <v>-1219.59</v>
+      </c>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="23" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>All trades</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="24" t="n"/>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n">
+        <v>236.98</v>
+      </c>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="23" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Winners</t>
-        </is>
-      </c>
-      <c r="B30" s="25" t="inlineStr">
-        <is>
-          <t>2 (18.2%)</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="24" t="n"/>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="n">
+        <v>-1456.57</v>
+      </c>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="23" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Losers</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>9 (81.8%)</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="24" t="n"/>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="n">
+        <v>348.39</v>
+      </c>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="23" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Net P&amp;L (Rs)</t>
-        </is>
-      </c>
-      <c r="B32" s="27" t="n">
-        <v>-1515.48</v>
-      </c>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="24" t="n"/>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="n">
+        <v>-174.23</v>
+      </c>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="23" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Total Profit (Rs)</t>
-        </is>
-      </c>
-      <c r="B33" s="26" t="n">
-        <v>1040.37</v>
-      </c>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="24" t="n"/>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n">
+        <v>-10.42</v>
+      </c>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="23" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Total Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B34" s="27" t="n">
-        <v>-2555.85</v>
-      </c>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="24" t="n"/>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>236.98</v>
+      </c>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="23" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Transaction costs (Rs)</t>
-        </is>
-      </c>
-      <c r="B35" s="28" t="n">
-        <v>508.23</v>
-      </c>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="24" t="n"/>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="23" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (Rs)</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="n">
-        <v>-137.77</v>
-      </c>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="24" t="n"/>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="n">
+        <v>-242.76</v>
+      </c>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="23" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Avg Profit/Loss per trade (% of premium)</t>
-        </is>
-      </c>
-      <c r="B37" s="29" t="n">
-        <v>-6.91</v>
-      </c>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="24" t="n"/>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="n">
+        <v>-14.85</v>
+      </c>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="23" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (Rs)</t>
+          <t>Largest Win (Rs)</t>
         </is>
       </c>
       <c r="B38" s="26" t="n">
-        <v>520.1799999999999</v>
-      </c>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="24" t="n"/>
+        <v>236.98</v>
+      </c>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="23" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Avg Win (% of premium)</t>
-        </is>
-      </c>
-      <c r="B39" s="30" t="n">
-        <v>54.92</v>
-      </c>
-      <c r="C39" s="23" t="n"/>
-      <c r="D39" s="24" t="n"/>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="n">
+        <v>-295.95</v>
+      </c>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="23" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B40" s="27" t="n">
-        <v>-283.98</v>
-      </c>
-      <c r="C40" s="23" t="n"/>
-      <c r="D40" s="24" t="n"/>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="23" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Avg Loss (% of premium)</t>
-        </is>
-      </c>
-      <c r="B41" s="31" t="n">
-        <v>-20.65</v>
-      </c>
-      <c r="C41" s="23" t="n"/>
-      <c r="D41" s="24" t="n"/>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="23" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Largest Win (Rs)</t>
-        </is>
-      </c>
-      <c r="B42" s="26" t="n">
-        <v>548.01</v>
-      </c>
-      <c r="C42" s="23" t="n"/>
-      <c r="D42" s="24" t="n"/>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="n">
+        <v>-295.95</v>
+      </c>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="23" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Largest Loss (Rs)</t>
-        </is>
-      </c>
-      <c r="B43" s="27" t="n">
-        <v>-358.86</v>
-      </c>
-      <c r="C43" s="23" t="n"/>
-      <c r="D43" s="24" t="n"/>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="n">
+        <v>-1225.26</v>
+      </c>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="23" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Wins</t>
-        </is>
-      </c>
-      <c r="B44" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="24" t="n"/>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B44" s="30" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="23" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Max Consecutive Losses</t>
-        </is>
-      </c>
-      <c r="B45" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="C45" s="23" t="n"/>
-      <c r="D45" s="24" t="n"/>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="23" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Max trade drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B46" s="27" t="n">
-        <v>-358.86</v>
-      </c>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="24" t="n"/>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B46" s="31" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="23" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (Rs)</t>
-        </is>
-      </c>
-      <c r="B47" s="27" t="n">
-        <v>-1988.15</v>
-      </c>
-      <c r="C47" s="23" t="n"/>
-      <c r="D47" s="24" t="n"/>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B47" s="31" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="23" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Max system drawdown (%)</t>
+          <t>Sharpe Ratio (annualized)</t>
         </is>
       </c>
       <c r="B48" s="31" t="n">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="C48" s="23" t="n"/>
-      <c r="D48" s="24" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Recovery Factor</t>
-        </is>
-      </c>
-      <c r="B49" s="32" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="C49" s="23" t="n"/>
-      <c r="D49" s="24" t="n"/>
+        <v>-12.48</v>
+      </c>
+      <c r="C48" s="22" t="n"/>
+      <c r="D48" s="23" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Profit Factor</t>
-        </is>
-      </c>
-      <c r="B50" s="32" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="C50" s="23" t="n"/>
-      <c r="D50" s="24" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Payoff Ratio (avg win / avg loss)</t>
-        </is>
-      </c>
-      <c r="B51" s="32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="C51" s="23" t="n"/>
-      <c r="D51" s="24" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Sharpe Ratio (annualized)</t>
-        </is>
-      </c>
-      <c r="B52" s="32" t="n">
-        <v>-9.4</v>
-      </c>
-      <c r="C52" s="23" t="n"/>
-      <c r="D52" s="24" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
@@ -3274,22 +2500,22 @@
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B49:D49"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B51:D51"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="B48:D48"/>

--- a/reports/latest_backtest_dashboard.xlsx
+++ b/reports/latest_backtest_dashboard.xlsx
@@ -20,8 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;-#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0;-#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot;%&quot;"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,12 +53,30 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="000B8A00"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000B8A00"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,8 +89,20 @@
         <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE8E8"/>
+        <bgColor rgb="00FDE8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -89,11 +124,55 @@
         <color rgb="00B7B7B7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -101,8 +180,51 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -532,31 +654,23 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>vwap_ema_momentum (EMA9/13) [5m]</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>-0.01480658481386824</v>
       </c>
     </row>
     <row r="5">
@@ -570,25 +684,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -605,25 +719,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -641,31 +755,23 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>-0.01480658481386824</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Each index sheet shows ONLY its single best-performing strategy/EMA combo from this backtest -- not all combos combined (that would double-count the same time period across competing strategies). See latest_backtest_summary.xlsx for every combo.</t>
         </is>
@@ -683,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -706,18 +812,707 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NIFTY -- best:  -- PAPER TRADE, NOT REAL MONEY</t>
+          <t>NIFTY -- best: vwap_ema_momentum (EMA9/13) [5m] -- PAPER TRADE, NOT REAL MONEY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>MONTHLY returns (% of capital at start of month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Yr %</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Yr P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="13" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="14" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="13" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="15" t="n">
+        <v>0.01385750000000008</v>
+      </c>
+      <c r="O5" s="16" t="n">
+        <v>277.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="17" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="15" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="17" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-Mar</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="18" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>-75.34</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-May</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="20" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>548.01</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-Oct</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="18" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>-195.52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>23-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="13" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="18" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>-75.34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="14" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="20" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>548.01</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>12-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="13" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="18" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>-195.52</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="23" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2 (40.0%)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="23" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>3 (60.0%)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="23" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="23" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>1040.37</v>
+      </c>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="23" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n">
+        <v>-763.22</v>
+      </c>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="23" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="n">
+        <v>143.6</v>
+      </c>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="23" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="23" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="23" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="n">
+        <v>520.1799999999999</v>
+      </c>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="23" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="23" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n">
+        <v>-254.41</v>
+      </c>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="23" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="n">
+        <v>-32.27</v>
+      </c>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="23" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="n">
+        <v>548.01</v>
+      </c>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="23" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n">
+        <v>-299.45</v>
+      </c>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="23" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="23" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="23" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n">
+        <v>-299.45</v>
+      </c>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="23" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n">
+        <v>-299.45</v>
+      </c>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="23" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="23" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="23" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B42" s="31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="23" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="23" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="23" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B39:D39"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -757,7 +1552,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
         </is>
@@ -803,7 +1598,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
         </is>
@@ -821,7 +1616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -849,13 +1644,702 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>No trades yet for this index -- this fills in automatically as the bot trades.</t>
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>MONTHLY returns (% of capital at start of month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Yr %</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Yr P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="13" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="14" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="13" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="15" t="n">
+        <v>0.01385750000000008</v>
+      </c>
+      <c r="O5" s="16" t="n">
+        <v>277.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Avg</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="17" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="15" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="17" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>WEEKLY returns (% of capital at start of that week; weeks split at month edges)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Month %</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Month P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-Mar</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="18" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="I10" s="19" t="n">
+        <v>-75.34</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-May</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="20" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>548.01</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-Oct</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="18" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="I12" s="19" t="n">
+        <v>-195.52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>DAILY returns (% of capital at start of that day; blank = no trade that day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Week starting (Mon)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Week %</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Week P&amp;L (Rs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>23-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="13" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="18" t="n">
+        <v>-0.003766999999999999</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>-75.34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="14" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="20" t="n">
+        <v>0.02750410797474085</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>548.01</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>12-Oct-2026</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="13" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="18" t="n">
+        <v>-0.009550293146912445</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>-195.52</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>STATISTICS (all trades for this index)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>All trades</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="23" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Winners</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2 (40.0%)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="23" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Losers</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>3 (60.0%)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="23" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Net P&amp;L (Rs)</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="23" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Total Profit (Rs)</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>1040.37</v>
+      </c>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="23" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Total Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="n">
+        <v>-763.22</v>
+      </c>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="23" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Transaction costs (Rs)</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="n">
+        <v>143.6</v>
+      </c>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="23" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (Rs)</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="23" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Avg Profit/Loss per trade (% of premium)</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="23" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="n">
+        <v>520.1799999999999</v>
+      </c>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="23" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Avg Win (% of premium)</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="23" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n">
+        <v>-254.41</v>
+      </c>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="23" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Avg Loss (% of premium)</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="n">
+        <v>-32.27</v>
+      </c>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="23" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Largest Win (Rs)</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="n">
+        <v>548.01</v>
+      </c>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="23" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Largest Loss (Rs)</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n">
+        <v>-299.45</v>
+      </c>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="23" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Wins</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="23" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Max Consecutive Losses</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="23" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Max trade drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n">
+        <v>-299.45</v>
+      </c>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="23" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (Rs)</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n">
+        <v>-299.45</v>
+      </c>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="23" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Max system drawdown (%)</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="23" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="23" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+      <c r="B42" s="31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="23" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Payoff Ratio (avg win / avg loss)</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="23" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio (annualized)</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="23" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Caveat: with only a handful of trades these numbers (Sharpe, profit factor, drawdown %) are not statistically reliable. Watch this over weeks/months before drawing conclusions.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B39:D39"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
